--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D568"/>
+  <dimension ref="A1:D522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -498,363 +498,363 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024/03/09</t>
+          <t>2024/03/08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024/03/10</t>
+          <t>2024/03/09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>101</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024/03/11</t>
+          <t>2024/03/10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>101</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024/03/12</t>
+          <t>2024/03/11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>101</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024/03/13</t>
+          <t>2024/03/12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>101</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024/03/14</t>
+          <t>2024/03/13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>101</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024/03/15</t>
+          <t>2024/03/13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>101</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024/03/16</t>
+          <t>2024/03/14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024/03/17</t>
+          <t>2024/03/15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024/03/18</t>
+          <t>2024/03/16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024/03/19</t>
+          <t>2024/03/17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024/03/20</t>
+          <t>2024/03/18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024/03/21</t>
+          <t>2024/03/19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024/03/22</t>
+          <t>2024/03/20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>101</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024/03/23</t>
+          <t>2024/03/21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024/03/24</t>
+          <t>2024/03/22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>101</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024/03/25</t>
+          <t>2024/03/23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>21</v>
       </c>
       <c r="D21" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024/03/26</t>
+          <t>2024/03/24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>101</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024/03/27</t>
+          <t>2024/03/25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024/03/28</t>
+          <t>2024/03/26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -867,12 +867,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024/03/29</t>
+          <t>2024/03/27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -885,12 +885,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024/03/30</t>
+          <t>2024/03/28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -903,12 +903,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024/03/31</t>
+          <t>2024/03/29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -921,12 +921,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024/04/01</t>
+          <t>2024/03/30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -939,12 +939,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024/04/02</t>
+          <t>2024/03/31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -957,12 +957,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024/04/03</t>
+          <t>2024/04/01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -975,12 +975,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024/04/04</t>
+          <t>2024/04/02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -993,12 +993,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024/04/05</t>
+          <t>2024/04/03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1011,12 +1011,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024/04/06</t>
+          <t>2024/04/04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1029,12 +1029,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024/04/07</t>
+          <t>2024/04/05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1047,12 +1047,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024/04/08</t>
+          <t>2024/04/06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1065,12 +1065,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024/04/09</t>
+          <t>2024/04/07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1083,12 +1083,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024/04/10</t>
+          <t>2024/04/08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1101,12 +1101,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024/04/11</t>
+          <t>2024/04/09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1119,12 +1119,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024/04/12</t>
+          <t>2024/04/10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1137,12 +1137,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024/04/13</t>
+          <t>2024/04/11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1155,12 +1155,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024/04/14</t>
+          <t>2024/04/12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1173,12 +1173,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024/04/15</t>
+          <t>2024/04/13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1191,12 +1191,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024/04/16</t>
+          <t>2024/04/14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1209,12 +1209,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024/04/17</t>
+          <t>2024/04/15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1227,12 +1227,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024/04/18</t>
+          <t>2024/04/16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1245,12 +1245,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024/04/19</t>
+          <t>2024/04/17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1263,16 +1263,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024/04/19</t>
+          <t>2024/04/18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D47" t="n">
         <v>101</v>
@@ -1281,12 +1281,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024/04/20</t>
+          <t>2024/04/19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1299,12 +1299,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024/04/21</t>
+          <t>2024/04/20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1317,12 +1317,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024/04/22</t>
+          <t>2024/04/21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1335,12 +1335,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024/04/23</t>
+          <t>2024/04/22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1353,12 +1353,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024/04/24</t>
+          <t>2024/04/23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1371,12 +1371,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024/04/25</t>
+          <t>2024/04/24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1389,12 +1389,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024/04/26</t>
+          <t>2024/04/25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1407,12 +1407,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024/04/27</t>
+          <t>2024/04/26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1425,12 +1425,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024/04/28</t>
+          <t>2024/04/27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1443,12 +1443,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024/04/29</t>
+          <t>2024/04/28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1461,12 +1461,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024/04/30</t>
+          <t>2024/04/29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1479,12 +1479,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024/05/01</t>
+          <t>2024/04/30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1497,16 +1497,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024/05/02</t>
+          <t>2024/05/01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D60" t="n">
         <v>101</v>
@@ -1515,12 +1515,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024/05/03</t>
+          <t>2024/05/02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1533,12 +1533,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024/05/04</t>
+          <t>2024/05/03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1551,12 +1551,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024/05/05</t>
+          <t>2024/05/04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1569,12 +1569,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024/05/06</t>
+          <t>2024/05/05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1587,12 +1587,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024/05/07</t>
+          <t>2024/05/06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1605,16 +1605,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024/05/08</t>
+          <t>2024/05/07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D66" t="n">
         <v>101</v>
@@ -1623,12 +1623,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024/05/09</t>
+          <t>2024/05/08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1641,12 +1641,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024/05/10</t>
+          <t>2024/05/09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1659,16 +1659,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2024/05/11</t>
+          <t>2024/05/10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D69" t="n">
         <v>101</v>
@@ -1677,12 +1677,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024/05/12</t>
+          <t>2024/05/11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1695,12 +1695,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2024/05/13</t>
+          <t>2024/05/12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1713,16 +1713,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2024/05/14</t>
+          <t>2024/05/13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D72" t="n">
         <v>101</v>
@@ -1740,57 +1740,57 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D73" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2024/05/14</t>
+          <t>2024/05/15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>21</v>
       </c>
       <c r="D74" t="n">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2024/05/15</t>
+          <t>2024/05/16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>21</v>
       </c>
       <c r="D75" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024/05/16</t>
+          <t>2024/05/17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1803,12 +1803,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2024/05/17</t>
+          <t>2024/05/18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1821,12 +1821,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2024/05/18</t>
+          <t>2024/05/19</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1839,16 +1839,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2024/05/19</t>
+          <t>2024/05/20</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
         <v>101</v>
@@ -1857,16 +1857,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2024/05/20</t>
+          <t>2024/05/21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D80" t="n">
         <v>101</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D81" t="n">
         <v>101</v>
@@ -1893,16 +1893,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2024/05/21</t>
+          <t>2024/05/22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D82" t="n">
         <v>101</v>
@@ -1911,12 +1911,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024/05/21</t>
+          <t>2024/05/23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1929,12 +1929,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2024/05/22</t>
+          <t>2024/05/24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1947,16 +1947,16 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2024/05/23</t>
+          <t>2024/05/25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D85" t="n">
         <v>101</v>
@@ -1965,12 +1965,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024/05/24</t>
+          <t>2024/05/26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1983,12 +1983,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2024/05/25</t>
+          <t>2024/05/27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2001,12 +2001,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2024/05/26</t>
+          <t>2024/05/28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2019,12 +2019,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2024/05/27</t>
+          <t>2024/05/29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2037,12 +2037,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024/05/28</t>
+          <t>2024/05/30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2055,12 +2055,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2024/05/29</t>
+          <t>2024/05/31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2073,12 +2073,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024/05/30</t>
+          <t>2024/06/01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2091,12 +2091,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2024/05/31</t>
+          <t>2024/06/02</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2109,12 +2109,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2024/06/01</t>
+          <t>2024/06/03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2127,16 +2127,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024/06/02</t>
+          <t>2024/06/04</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D95" t="n">
         <v>101</v>
@@ -2145,16 +2145,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2024/06/02</t>
+          <t>2024/06/05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D96" t="n">
         <v>101</v>
@@ -2163,12 +2163,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2024/06/02</t>
+          <t>2024/06/06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2181,16 +2181,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2024/06/03</t>
+          <t>2024/06/08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
         <v>101</v>
@@ -2199,16 +2199,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2024/06/03</t>
+          <t>2024/06/08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D99" t="n">
         <v>101</v>
@@ -2217,12 +2217,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2024/06/03</t>
+          <t>2024/06/09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2235,16 +2235,16 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2024/06/04</t>
+          <t>2024/06/10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D101" t="n">
         <v>101</v>
@@ -2253,7 +2253,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024/06/04</t>
+          <t>2024/06/11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2271,12 +2271,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024/06/04</t>
+          <t>2024/06/12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2289,12 +2289,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2024/06/05</t>
+          <t>2024/06/13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2307,12 +2307,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2024/06/06</t>
+          <t>2024/06/14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2325,16 +2325,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2024/06/07</t>
+          <t>2024/06/16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
         <v>101</v>
@@ -2343,16 +2343,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2024/06/07</t>
+          <t>2024/06/16</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>101</v>
@@ -2361,12 +2361,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024/06/07</t>
+          <t>2024/06/17</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2379,16 +2379,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024/06/08</t>
+          <t>2024/06/18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D109" t="n">
         <v>101</v>
@@ -2397,16 +2397,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2024/06/08</t>
+          <t>2024/06/19</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D110" t="n">
         <v>101</v>
@@ -2415,12 +2415,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024/06/08</t>
+          <t>2024/06/20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2433,12 +2433,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024/06/09</t>
+          <t>2024/06/21</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2451,12 +2451,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024/06/10</t>
+          <t>2024/06/22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2469,16 +2469,16 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024/06/11</t>
+          <t>2024/06/23</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D114" t="n">
         <v>101</v>
@@ -2487,16 +2487,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2024/06/12</t>
+          <t>2024/06/24</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D115" t="n">
         <v>101</v>
@@ -2505,12 +2505,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2024/06/13</t>
+          <t>2024/06/25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2523,12 +2523,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2024/06/14</t>
+          <t>2024/06/26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2541,16 +2541,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2024/06/15</t>
+          <t>2024/06/27</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D118" t="n">
         <v>101</v>
@@ -2559,12 +2559,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2024/06/16</t>
+          <t>2024/06/28</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2577,12 +2577,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2024/06/17</t>
+          <t>2024/06/29</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2595,12 +2595,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2024/06/18</t>
+          <t>2024/06/30</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2613,12 +2613,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2024/06/19</t>
+          <t>2024/07/01</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2631,12 +2631,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2024/06/20</t>
+          <t>2024/07/02</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2649,12 +2649,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2024/06/21</t>
+          <t>2024/07/03</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2667,12 +2667,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2024/06/22</t>
+          <t>2024/07/04</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2685,16 +2685,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2024/06/23</t>
+          <t>2024/07/05</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D126" t="n">
         <v>101</v>
@@ -2703,12 +2703,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2024/06/24</t>
+          <t>2024/07/06</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2721,12 +2721,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2024/06/25</t>
+          <t>2024/07/07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2739,12 +2739,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2024/06/26</t>
+          <t>2024/07/08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2757,12 +2757,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2024/06/27</t>
+          <t>2024/07/09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2775,12 +2775,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2024/06/28</t>
+          <t>2024/07/10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2793,12 +2793,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2024/06/29</t>
+          <t>2024/07/11</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2811,12 +2811,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2024/06/30</t>
+          <t>2024/07/12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2829,16 +2829,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2024/07/01</t>
+          <t>2024/07/13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D134" t="n">
         <v>101</v>
@@ -2847,16 +2847,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2024/07/02</t>
+          <t>2024/07/14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D135" t="n">
         <v>101</v>
@@ -2865,12 +2865,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2024/07/03</t>
+          <t>2024/07/15</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2883,16 +2883,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024/07/04</t>
+          <t>2024/07/16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D137" t="n">
         <v>101</v>
@@ -2901,12 +2901,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2024/07/05</t>
+          <t>2024/07/17</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2919,12 +2919,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2024/07/06</t>
+          <t>2024/07/18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2937,16 +2937,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2024/07/07</t>
+          <t>2024/07/19</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D140" t="n">
         <v>101</v>
@@ -2955,12 +2955,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2024/07/07</t>
+          <t>2024/07/20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2973,16 +2973,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2024/07/08</t>
+          <t>2024/07/21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D142" t="n">
         <v>101</v>
@@ -2991,7 +2991,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2024/07/08</t>
+          <t>2024/07/22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2024/07/09</t>
+          <t>2024/07/23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2024/07/10</t>
+          <t>2024/07/24</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D145" t="n">
         <v>101</v>
@@ -3045,7 +3045,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2024/07/11</t>
+          <t>2024/07/25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D146" t="n">
         <v>101</v>
@@ -3063,16 +3063,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2024/07/11</t>
+          <t>2024/07/26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D147" t="n">
         <v>101</v>
@@ -3081,12 +3081,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2024/07/12</t>
+          <t>2024/07/27</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -3099,12 +3099,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2024/07/13</t>
+          <t>2024/07/28</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3117,12 +3117,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2024/07/14</t>
+          <t>2024/07/29</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -3135,12 +3135,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2024/07/15</t>
+          <t>2024/07/30</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3153,12 +3153,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2024/07/16</t>
+          <t>2024/07/31</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -3171,12 +3171,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2024/07/17</t>
+          <t>2024/08/01</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3189,16 +3189,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2024/07/18</t>
+          <t>2024/08/02</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D154" t="n">
         <v>101</v>
@@ -3207,12 +3207,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2024/07/19</t>
+          <t>2024/08/03</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -3225,16 +3225,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2024/07/20</t>
+          <t>2024/08/04</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D156" t="n">
         <v>101</v>
@@ -3243,12 +3243,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2024/07/20</t>
+          <t>2024/08/05</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3261,12 +3261,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2024/07/21</t>
+          <t>2024/08/06</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -3279,16 +3279,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2024/07/22</t>
+          <t>2024/08/07</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D159" t="n">
         <v>101</v>
@@ -3297,12 +3297,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2024/07/23</t>
+          <t>2024/08/08</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -3315,12 +3315,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2024/07/24</t>
+          <t>2024/08/09</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -3333,12 +3333,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2024/07/25</t>
+          <t>2024/08/10</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3351,12 +3351,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2024/07/26</t>
+          <t>2024/08/11</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3369,12 +3369,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2024/07/27</t>
+          <t>2024/08/12</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3387,16 +3387,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2024/07/28</t>
+          <t>2024/08/13</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D165" t="n">
         <v>101</v>
@@ -3405,16 +3405,16 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2024/07/29</t>
+          <t>2024/08/14</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D166" t="n">
         <v>101</v>
@@ -3423,16 +3423,16 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2024/07/29</t>
+          <t>2024/08/15</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D167" t="n">
         <v>101</v>
@@ -3441,12 +3441,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2024/07/29</t>
+          <t>2024/08/16</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3459,12 +3459,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2024/07/30</t>
+          <t>2024/08/17</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3477,16 +3477,16 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2024/07/31</t>
+          <t>2024/08/18</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D170" t="n">
         <v>101</v>
@@ -3495,16 +3495,16 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2024/08/02</t>
+          <t>2024/08/19</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D171" t="n">
         <v>101</v>
@@ -3513,12 +3513,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2024/08/02</t>
+          <t>2024/08/20</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3531,16 +3531,16 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2024/08/03</t>
+          <t>2024/08/21</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D173" t="n">
         <v>101</v>
@@ -3549,12 +3549,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2024/08/04</t>
+          <t>2024/08/21</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3567,12 +3567,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2024/08/05</t>
+          <t>2024/08/22</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3585,12 +3585,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2024/08/06</t>
+          <t>2024/08/23</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3603,12 +3603,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2024/08/07</t>
+          <t>2024/08/24</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3621,12 +3621,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2024/08/08</t>
+          <t>2024/08/25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3639,12 +3639,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2024/08/09</t>
+          <t>2024/08/26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3657,12 +3657,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2024/08/10</t>
+          <t>2024/08/27</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3675,16 +3675,16 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2024/08/11</t>
+          <t>2024/08/27</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D181" t="n">
         <v>101</v>
@@ -3693,12 +3693,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2024/08/12</t>
+          <t>2024/08/28</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3711,12 +3711,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2024/08/13</t>
+          <t>2024/08/29</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3729,12 +3729,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2024/08/14</t>
+          <t>2024/08/30</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3747,16 +3747,16 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2024/08/16</t>
+          <t>2024/08/31</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D185" t="n">
         <v>101</v>
@@ -3765,12 +3765,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2024/08/17</t>
+          <t>2024/09/01</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3783,12 +3783,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2024/08/17</t>
+          <t>2024/09/02</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3801,12 +3801,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2024/08/18</t>
+          <t>2024/09/03</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3819,12 +3819,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2024/08/19</t>
+          <t>2024/09/04</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3837,12 +3837,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2024/08/20</t>
+          <t>2024/09/05</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3855,12 +3855,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2024/08/21</t>
+          <t>2024/09/06</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3873,12 +3873,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2024/08/22</t>
+          <t>2024/09/07</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3891,16 +3891,16 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2024/08/23</t>
+          <t>2024/09/08</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D193" t="n">
         <v>101</v>
@@ -3909,16 +3909,16 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2024/08/24</t>
+          <t>2024/09/09</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D194" t="n">
         <v>101</v>
@@ -3927,12 +3927,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2024/08/25</t>
+          <t>2024/09/10</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3945,12 +3945,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2024/08/26</t>
+          <t>2024/09/11</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3963,16 +3963,16 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2024/08/27</t>
+          <t>2024/09/12</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D197" t="n">
         <v>101</v>
@@ -3981,12 +3981,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2024/08/28</t>
+          <t>2024/09/13</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3999,12 +3999,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2024/08/29</t>
+          <t>2024/09/14</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -4017,12 +4017,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2024/08/30</t>
+          <t>2024/09/15</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -4035,12 +4035,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2024/08/31</t>
+          <t>2024/09/16</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -4053,12 +4053,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2024/09/01</t>
+          <t>2024/09/17</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -4071,12 +4071,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2024/09/02</t>
+          <t>2024/09/18</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -4089,12 +4089,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2024/09/03</t>
+          <t>2024/09/19</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -4107,12 +4107,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2024/09/04</t>
+          <t>2024/09/20</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -4125,12 +4125,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2024/09/05</t>
+          <t>2024/09/21</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -4143,12 +4143,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2024/09/06</t>
+          <t>2024/09/22</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -4161,16 +4161,16 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2024/09/07</t>
+          <t>2024/09/23</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D208" t="n">
         <v>101</v>
@@ -4179,12 +4179,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2024/09/08</t>
+          <t>2024/09/23</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -4197,12 +4197,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2024/09/09</t>
+          <t>2024/09/24</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -4215,12 +4215,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2024/09/10</t>
+          <t>2024/09/25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -4233,12 +4233,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2024/09/11</t>
+          <t>2024/09/26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -4251,12 +4251,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2024/09/12</t>
+          <t>2024/09/27</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -4269,12 +4269,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2024/09/13</t>
+          <t>2024/09/28</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -4287,12 +4287,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2024/09/14</t>
+          <t>2024/09/29</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -4305,12 +4305,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2024/09/15</t>
+          <t>2024/09/30</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -4323,12 +4323,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2024/09/16</t>
+          <t>2024/10/01</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -4341,12 +4341,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2024/09/17</t>
+          <t>2024/10/02</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -4359,12 +4359,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2024/09/18</t>
+          <t>2024/10/03</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -4377,12 +4377,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2024/09/19</t>
+          <t>2024/10/04</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -4395,12 +4395,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2024/09/20</t>
+          <t>2024/10/05</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -4413,12 +4413,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2024/09/21</t>
+          <t>2024/10/06</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -4431,16 +4431,16 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2024/09/22</t>
+          <t>2024/10/07</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D223" t="n">
         <v>101</v>
@@ -4449,12 +4449,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2024/09/23</t>
+          <t>2024/10/08</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -4467,16 +4467,16 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2024/09/24</t>
+          <t>2024/10/09</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D225" t="n">
         <v>101</v>
@@ -4485,12 +4485,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2024/09/25</t>
+          <t>2024/10/10</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -4503,12 +4503,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2024/09/26</t>
+          <t>2024/10/11</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -4521,12 +4521,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2024/09/27</t>
+          <t>2024/10/12</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -4539,12 +4539,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2024/09/28</t>
+          <t>2024/10/13</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -4557,12 +4557,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2024/09/29</t>
+          <t>2024/10/14</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4575,12 +4575,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2024/09/30</t>
+          <t>2024/10/15</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4593,12 +4593,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2024/10/01</t>
+          <t>2024/10/16</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4611,12 +4611,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2024/10/02</t>
+          <t>2024/10/17</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4629,12 +4629,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2024/10/03</t>
+          <t>2024/10/18</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4647,12 +4647,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2024/10/04</t>
+          <t>2024/10/19</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4665,12 +4665,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2024/10/05</t>
+          <t>2024/10/20</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4683,12 +4683,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2024/10/06</t>
+          <t>2024/10/21</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4701,12 +4701,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2024/10/07</t>
+          <t>2024/10/22</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4719,12 +4719,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2024/10/08</t>
+          <t>2024/10/23</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4737,12 +4737,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2024/10/09</t>
+          <t>2024/10/24</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4755,12 +4755,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2024/10/10</t>
+          <t>2024/10/25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4773,12 +4773,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2024/10/11</t>
+          <t>2024/10/26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4791,16 +4791,16 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2024/10/12</t>
+          <t>2024/10/27</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D243" t="n">
         <v>101</v>
@@ -4809,16 +4809,16 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2024/10/12</t>
+          <t>2024/10/28</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D244" t="n">
         <v>101</v>
@@ -4827,12 +4827,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2024/10/12</t>
+          <t>2024/10/29</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4845,16 +4845,16 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2024/10/13</t>
+          <t>2024/10/30</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D246" t="n">
         <v>101</v>
@@ -4863,12 +4863,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2024/10/14</t>
+          <t>2024/10/31</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4881,12 +4881,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2024/10/15</t>
+          <t>2024/11/01</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4899,12 +4899,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2024/10/16</t>
+          <t>2024/11/02</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4917,16 +4917,16 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2024/10/17</t>
+          <t>2024/11/03</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D250" t="n">
         <v>101</v>
@@ -4935,16 +4935,16 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2024/10/18</t>
+          <t>2024/11/04</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D251" t="n">
         <v>101</v>
@@ -4953,16 +4953,16 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2024/10/19</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D252" t="n">
         <v>101</v>
@@ -4971,16 +4971,16 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2024/10/20</t>
+          <t>2024/11/06</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D253" t="n">
         <v>101</v>
@@ -4989,16 +4989,16 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2024/10/21</t>
+          <t>2024/11/07</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D254" t="n">
         <v>101</v>
@@ -5007,16 +5007,16 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2024/10/22</t>
+          <t>2024/11/08</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D255" t="n">
         <v>101</v>
@@ -5025,16 +5025,16 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2024/10/23</t>
+          <t>2024/11/09</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D256" t="n">
         <v>101</v>
@@ -5043,16 +5043,16 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2024/10/24</t>
+          <t>2024/11/10</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D257" t="n">
         <v>101</v>
@@ -5061,16 +5061,16 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2024/10/25</t>
+          <t>2024/11/11</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D258" t="n">
         <v>101</v>
@@ -5079,16 +5079,16 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2024/10/26</t>
+          <t>2024/11/12</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D259" t="n">
         <v>101</v>
@@ -5097,16 +5097,16 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2024/10/27</t>
+          <t>2024/11/13</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D260" t="n">
         <v>101</v>
@@ -5115,16 +5115,16 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2024/10/28</t>
+          <t>2024/11/14</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D261" t="n">
         <v>101</v>
@@ -5133,16 +5133,16 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2024/10/29</t>
+          <t>2024/11/15</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D262" t="n">
         <v>101</v>
@@ -5151,16 +5151,16 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2024/10/30</t>
+          <t>2024/11/16</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D263" t="n">
         <v>101</v>
@@ -5169,16 +5169,16 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2024/10/31</t>
+          <t>2024/11/17</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D264" t="n">
         <v>101</v>
@@ -5187,16 +5187,16 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2024/11/01</t>
+          <t>2024/11/18</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D265" t="n">
         <v>101</v>
@@ -5205,16 +5205,16 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2024/11/02</t>
+          <t>2024/11/19</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D266" t="n">
         <v>101</v>
@@ -5223,16 +5223,16 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2024/11/03</t>
+          <t>2024/11/20</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D267" t="n">
         <v>101</v>
@@ -5241,16 +5241,16 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2024/11/04</t>
+          <t>2024/11/21</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D268" t="n">
         <v>101</v>
@@ -5259,12 +5259,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>2024/11/22</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -5277,12 +5277,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2024/11/06</t>
+          <t>2024/11/23</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -5295,12 +5295,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2024/11/07</t>
+          <t>2024/11/24</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -5313,12 +5313,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2024/11/08</t>
+          <t>2024/11/25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -5331,12 +5331,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2024/11/09</t>
+          <t>2024/11/26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -5349,12 +5349,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2024/11/10</t>
+          <t>2024/11/27</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -5367,12 +5367,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2024/11/11</t>
+          <t>2024/11/28</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -5385,12 +5385,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2024/11/12</t>
+          <t>2024/11/29</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -5403,12 +5403,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2024/11/13</t>
+          <t>2024/11/30</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -5421,12 +5421,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2024/11/14</t>
+          <t>2024/12/01</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -5439,12 +5439,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2024/11/15</t>
+          <t>2024/12/02</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -5457,12 +5457,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2024/11/16</t>
+          <t>2024/12/03</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -5475,12 +5475,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2024/11/17</t>
+          <t>2024/12/04</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -5493,12 +5493,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2024/11/18</t>
+          <t>2024/12/05</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -5511,16 +5511,16 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>2024/12/06</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D283" t="n">
         <v>101</v>
@@ -5529,12 +5529,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2024/11/20</t>
+          <t>2024/12/07</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -5547,12 +5547,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2024/11/21</t>
+          <t>2024/12/08</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -5565,12 +5565,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2024/11/22</t>
+          <t>2024/12/09</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -5583,12 +5583,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2024/11/23</t>
+          <t>2024/12/10</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -5601,12 +5601,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2024/11/24</t>
+          <t>2024/12/11</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -5619,12 +5619,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2024/11/25</t>
+          <t>2024/12/12</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -5637,12 +5637,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2024/11/26</t>
+          <t>2024/12/13</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -5655,12 +5655,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2024/11/27</t>
+          <t>2024/12/14</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -5673,12 +5673,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2024/11/28</t>
+          <t>2024/12/15</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5691,12 +5691,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2024/11/29</t>
+          <t>2024/12/16</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -5709,12 +5709,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2024/11/30</t>
+          <t>2024/12/17</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -5727,12 +5727,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2024/12/01</t>
+          <t>2024/12/18</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -5745,12 +5745,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2024/12/02</t>
+          <t>2024/12/19</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5763,12 +5763,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2024/12/03</t>
+          <t>2024/12/20</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -5781,16 +5781,16 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2024/12/04</t>
+          <t>2024/12/21</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D298" t="n">
         <v>101</v>
@@ -5799,12 +5799,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2024/12/05</t>
+          <t>2024/12/22</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5817,16 +5817,16 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2024/12/06</t>
+          <t>2024/12/23</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D300" t="n">
         <v>101</v>
@@ -5835,12 +5835,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2024/12/07</t>
+          <t>2024/12/24</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5853,16 +5853,16 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2024/12/09</t>
+          <t>2024/12/25</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D302" t="n">
         <v>101</v>
@@ -5871,12 +5871,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2024/12/09</t>
+          <t>2024/12/26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5889,12 +5889,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2024/12/10</t>
+          <t>2024/12/27</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5907,12 +5907,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2024/12/11</t>
+          <t>2024/12/28</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5925,12 +5925,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2024/12/12</t>
+          <t>2024/12/29</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5943,12 +5943,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2024/12/13</t>
+          <t>2024/12/30</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5961,12 +5961,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2024/12/14</t>
+          <t>2024/12/31</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5979,12 +5979,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2024/12/15</t>
+          <t>2025/01/01</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5997,12 +5997,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2024/12/16</t>
+          <t>2025/01/02</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -6015,12 +6015,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2024/12/17</t>
+          <t>2025/01/03</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -6033,12 +6033,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2024/12/18</t>
+          <t>2025/01/04</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -6051,12 +6051,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2024/12/19</t>
+          <t>2025/01/05</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -6069,12 +6069,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2024/12/20</t>
+          <t>2025/01/06</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -6087,12 +6087,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2024/12/21</t>
+          <t>2025/01/07</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -6105,12 +6105,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2024/12/22</t>
+          <t>2025/01/08</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -6123,12 +6123,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2024/12/23</t>
+          <t>2025/01/09</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -6141,12 +6141,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024/12/24</t>
+          <t>2025/01/10</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -6159,12 +6159,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2024/12/25</t>
+          <t>2025/01/11</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -6177,12 +6177,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024/12/26</t>
+          <t>2025/01/12</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -6195,12 +6195,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024/12/27</t>
+          <t>2025/01/13</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -6213,12 +6213,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024/12/28</t>
+          <t>2025/01/14</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -6231,12 +6231,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024/12/29</t>
+          <t>2025/01/15</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -6249,12 +6249,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024/12/30</t>
+          <t>2025/01/16</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -6267,12 +6267,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024/12/31</t>
+          <t>2025/01/17</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -6285,12 +6285,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2025/01/01</t>
+          <t>2025/01/18</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -6303,12 +6303,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2025/01/02</t>
+          <t>2025/01/19</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -6321,12 +6321,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2025/01/03</t>
+          <t>2025/01/20</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -6339,12 +6339,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2025/01/04</t>
+          <t>2025/01/21</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -6357,12 +6357,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2025/01/05</t>
+          <t>2025/01/22</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -6375,12 +6375,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2025/01/06</t>
+          <t>2025/01/23</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -6393,12 +6393,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2025/01/07</t>
+          <t>2025/01/24</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -6411,12 +6411,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2025/01/08</t>
+          <t>2025/01/25</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -6429,12 +6429,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2025/01/09</t>
+          <t>2025/01/26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -6447,12 +6447,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2025/01/10</t>
+          <t>2025/01/27</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -6465,12 +6465,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2025/01/11</t>
+          <t>2025/01/28</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -6483,12 +6483,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2025/01/12</t>
+          <t>2025/01/29</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -6501,12 +6501,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2025/01/13</t>
+          <t>2025/01/30</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -6519,12 +6519,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2025/01/14</t>
+          <t>2025/01/31</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -6537,12 +6537,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2025/01/15</t>
+          <t>2025/02/01</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -6555,12 +6555,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2025/01/16</t>
+          <t>2025/02/02</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -6573,16 +6573,16 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2025/01/17</t>
+          <t>2025/02/03</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D342" t="n">
         <v>101</v>
@@ -6591,12 +6591,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2025/01/18</t>
+          <t>2025/02/03</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -6609,12 +6609,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2025/01/19</t>
+          <t>2025/02/04</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -6627,16 +6627,16 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2025/01/20</t>
+          <t>2025/02/05</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D345" t="n">
         <v>101</v>
@@ -6645,12 +6645,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2025/01/21</t>
+          <t>2025/02/06</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -6663,12 +6663,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2025/01/22</t>
+          <t>2025/02/07</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -6681,12 +6681,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2025/01/23</t>
+          <t>2025/02/08</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -6699,12 +6699,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2025/01/24</t>
+          <t>2025/02/09</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -6717,12 +6717,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2025/01/25</t>
+          <t>2025/02/10</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -6735,12 +6735,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2025/01/26</t>
+          <t>2025/02/11</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -6753,12 +6753,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2025/01/27</t>
+          <t>2025/02/12</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -6771,12 +6771,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2025/01/28</t>
+          <t>2025/02/13</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -6789,12 +6789,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2025/01/29</t>
+          <t>2025/02/14</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6807,12 +6807,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2025/01/30</t>
+          <t>2025/02/15</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -6825,12 +6825,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2025/01/31</t>
+          <t>2025/02/16</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -6843,12 +6843,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2025/02/01</t>
+          <t>2025/02/17</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -6861,12 +6861,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2025/02/02</t>
+          <t>2025/02/18</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -6879,16 +6879,16 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2025/02/03</t>
+          <t>2025/02/19</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D359" t="n">
         <v>101</v>
@@ -6897,12 +6897,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2025/02/03</t>
+          <t>2025/02/19</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6915,12 +6915,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2025/02/04</t>
+          <t>2025/02/20</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6933,12 +6933,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2025/02/05</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6951,16 +6951,16 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2025/02/05</t>
+          <t>2025/02/22</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D363" t="n">
         <v>101</v>
@@ -6969,12 +6969,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2025/02/06</t>
+          <t>2025/02/23</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6987,12 +6987,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/02/24</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -7005,16 +7005,16 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2025/02/08</t>
+          <t>2025/02/25</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D366" t="n">
         <v>101</v>
@@ -7023,12 +7023,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2025/02/09</t>
+          <t>2025/02/26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -7041,12 +7041,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2025/02/10</t>
+          <t>2025/02/27</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -7059,12 +7059,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2025/02/11</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -7077,30 +7077,30 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2025/02/12</t>
+          <t>2025/03/01</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D370" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2025/02/12</t>
+          <t>2025/03/02</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -7113,12 +7113,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2025/02/13</t>
+          <t>2025/03/03</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -7131,12 +7131,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>2025/03/04</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -7149,16 +7149,16 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2025/02/15</t>
+          <t>2025/03/05</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D374" t="n">
         <v>101</v>
@@ -7167,12 +7167,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2025/02/16</t>
+          <t>2025/03/06</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -7185,12 +7185,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2025/02/17</t>
+          <t>2025/03/07</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -7203,12 +7203,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2025/02/18</t>
+          <t>2025/03/08</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -7221,16 +7221,16 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2025/02/19</t>
+          <t>2025/03/09</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D378" t="n">
         <v>101</v>
@@ -7239,16 +7239,16 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2025/02/19</t>
+          <t>2025/03/10</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D379" t="n">
         <v>101</v>
@@ -7257,16 +7257,16 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2025/02/20</t>
+          <t>2025/03/11</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D380" t="n">
         <v>101</v>
@@ -7275,16 +7275,16 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2025/02/21</t>
+          <t>2025/03/12</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D381" t="n">
         <v>101</v>
@@ -7293,12 +7293,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2025/02/22</t>
+          <t>2025/03/13</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -7311,16 +7311,16 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2025/02/22</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D383" t="n">
         <v>101</v>
@@ -7329,16 +7329,16 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2025/02/23</t>
+          <t>2025/03/15</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D384" t="n">
         <v>101</v>
@@ -7347,16 +7347,16 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2025/02/24</t>
+          <t>2025/03/16</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D385" t="n">
         <v>101</v>
@@ -7365,12 +7365,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2025/02/25</t>
+          <t>2025/03/17</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -7383,7 +7383,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2025/02/25</t>
+          <t>2025/03/18</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D387" t="n">
         <v>101</v>
@@ -7401,7 +7401,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2025/02/26</t>
+          <t>2025/03/19</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D388" t="n">
         <v>101</v>
@@ -7419,7 +7419,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2025/02/27</t>
+          <t>2025/03/20</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -7437,16 +7437,16 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2025/02/27</t>
+          <t>2025/03/21</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D390" t="n">
         <v>101</v>
@@ -7455,16 +7455,16 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2025/03/22</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D391" t="n">
         <v>101</v>
@@ -7473,34 +7473,34 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2025/03/01</t>
+          <t>2025/03/23</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D392" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2025/03/02</t>
+          <t>2025/03/24</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D393" t="n">
         <v>101</v>
@@ -7509,16 +7509,16 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2025/03/03</t>
+          <t>2025/03/25</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D394" t="n">
         <v>101</v>
@@ -7527,16 +7527,16 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2025/03/04</t>
+          <t>2025/03/26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D395" t="n">
         <v>101</v>
@@ -7545,16 +7545,16 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2025/03/05</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D396" t="n">
         <v>101</v>
@@ -7563,16 +7563,16 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2025/03/05</t>
+          <t>2025/03/28</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D397" t="n">
         <v>101</v>
@@ -7581,16 +7581,16 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2025/03/06</t>
+          <t>2025/03/29</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D398" t="n">
         <v>101</v>
@@ -7599,16 +7599,16 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2025/03/07</t>
+          <t>2025/03/30</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D399" t="n">
         <v>101</v>
@@ -7617,34 +7617,34 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2025/03/08</t>
+          <t>2025/03/31</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D400" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2025/03/08</t>
+          <t>2025/04/01</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D401" t="n">
         <v>101</v>
@@ -7653,16 +7653,16 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2025/03/09</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D402" t="n">
         <v>101</v>
@@ -7671,30 +7671,30 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2025/03/09</t>
+          <t>2025/04/03</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D403" t="n">
-        <v>40</v>
+        <v>101</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2025/03/10</t>
+          <t>2025/04/04</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -7707,12 +7707,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2025/03/11</t>
+          <t>2025/04/05</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -7725,16 +7725,16 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2025/03/12</t>
+          <t>2025/04/06</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D406" t="n">
         <v>101</v>
@@ -7743,48 +7743,48 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2025/03/12</t>
+          <t>2025/04/07</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C407" t="n">
         <v>21</v>
       </c>
       <c r="D407" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2025/03/13</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D408" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2025/03/13</t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -7797,16 +7797,16 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2025/04/10</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D410" t="n">
         <v>101</v>
@@ -7815,12 +7815,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2025/03/15</t>
+          <t>2025/04/11</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -7833,12 +7833,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2025/03/16</t>
+          <t>2025/04/12</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -7851,12 +7851,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2025/03/17</t>
+          <t>2025/04/13</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -7869,12 +7869,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2025/03/18</t>
+          <t>2025/04/14</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -7887,12 +7887,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2025/03/19</t>
+          <t>2025/04/15</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -7905,12 +7905,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2025/03/20</t>
+          <t>2025/04/16</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -7923,12 +7923,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2025/03/21</t>
+          <t>2025/04/17</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -7941,16 +7941,16 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2025/03/22</t>
+          <t>2025/04/18</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D418" t="n">
         <v>101</v>
@@ -7959,12 +7959,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2025/03/23</t>
+          <t>2025/04/18</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -7977,12 +7977,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2025/03/24</t>
+          <t>2025/04/19</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -7995,12 +7995,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2025/03/25</t>
+          <t>2025/04/20</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -8013,16 +8013,16 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2025/03/26</t>
+          <t>2025/04/21</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D422" t="n">
         <v>101</v>
@@ -8031,12 +8031,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2025/03/26</t>
+          <t>2025/04/22</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -8049,16 +8049,16 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2025/03/27</t>
+          <t>2025/04/23</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D424" t="n">
         <v>101</v>
@@ -8067,7 +8067,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2025/03/27</t>
+          <t>2025/04/24</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -8085,7 +8085,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2025/03/28</t>
+          <t>2025/04/25</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -8103,7 +8103,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2025/03/29</t>
+          <t>2025/04/26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2025/03/30</t>
+          <t>2025/04/27</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -8139,7 +8139,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2025/03/31</t>
+          <t>2025/04/28</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -8157,7 +8157,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>2025/04/29</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -8175,7 +8175,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2025/04/02</t>
+          <t>2025/04/30</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -8193,7 +8193,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2025/04/03</t>
+          <t>2025/05/01</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -8211,7 +8211,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2025/04/04</t>
+          <t>2025/05/02</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -8229,7 +8229,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2025/04/05</t>
+          <t>2025/05/03</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -8247,7 +8247,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2025/04/06</t>
+          <t>2025/05/04</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -8265,7 +8265,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2025/04/07</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -8283,7 +8283,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>2025/05/06</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -8301,7 +8301,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2025/04/09</t>
+          <t>2025/05/07</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -8319,7 +8319,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2025/04/10</t>
+          <t>2025/05/08</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D439" t="n">
         <v>101</v>
@@ -8337,12 +8337,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2025/04/10</t>
+          <t>2025/05/09</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -8355,12 +8355,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2025/04/11</t>
+          <t>2025/05/10</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -8373,12 +8373,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2025/04/12</t>
+          <t>2025/05/11</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -8391,12 +8391,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2025/04/13</t>
+          <t>2025/05/12</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -8409,12 +8409,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2025/04/14</t>
+          <t>2025/05/13</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -8427,12 +8427,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2025/04/15</t>
+          <t>2025/05/14</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -8445,12 +8445,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2025/04/16</t>
+          <t>2025/05/15</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -8463,12 +8463,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2025/04/17</t>
+          <t>2025/05/16</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -8481,16 +8481,16 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2025/04/18</t>
+          <t>2025/05/17</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D448" t="n">
         <v>101</v>
@@ -8499,12 +8499,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2025/04/18</t>
+          <t>2025/05/18</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -8517,16 +8517,16 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2025/04/19</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D450" t="n">
         <v>101</v>
@@ -8535,12 +8535,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2025/04/20</t>
+          <t>2025/05/20</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -8553,12 +8553,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2025/04/21</t>
+          <t>2025/05/21</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -8571,12 +8571,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2025/04/22</t>
+          <t>2025/05/22</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -8589,16 +8589,16 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2025/04/23</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D454" t="n">
         <v>101</v>
@@ -8607,12 +8607,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2025/04/24</t>
+          <t>2025/05/24</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -8625,12 +8625,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2025/04/25</t>
+          <t>2025/05/25</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -8643,12 +8643,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2025/04/26</t>
+          <t>2025/05/26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -8661,12 +8661,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2025/04/27</t>
+          <t>2025/05/27</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -8679,12 +8679,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2025/04/28</t>
+          <t>2025/05/28</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -8697,12 +8697,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2025/04/29</t>
+          <t>2025/05/29</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -8715,12 +8715,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2025/04/30</t>
+          <t>2025/05/30</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -8733,16 +8733,16 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2025/05/01</t>
+          <t>2025/05/31</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D462" t="n">
         <v>101</v>
@@ -8751,12 +8751,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2025/05/01</t>
+          <t>2025/06/01</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -8769,12 +8769,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2025/05/02</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -8787,12 +8787,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2025/05/03</t>
+          <t>2025/06/03</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -8805,12 +8805,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2025/05/04</t>
+          <t>2025/06/04</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -8823,12 +8823,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2025/05/05</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -8841,12 +8841,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2025/05/06</t>
+          <t>2025/06/06</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -8859,16 +8859,16 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2025/05/07</t>
+          <t>2025/06/07</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D469" t="n">
         <v>101</v>
@@ -8877,12 +8877,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2025/05/07</t>
+          <t>2025/06/08</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -8895,12 +8895,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2025/05/08</t>
+          <t>2025/06/09</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -8913,12 +8913,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2025/05/09</t>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -8931,12 +8931,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2025/05/10</t>
+          <t>2025/06/11</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -8949,12 +8949,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2025/05/11</t>
+          <t>2025/06/12</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -8967,12 +8967,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2025/05/12</t>
+          <t>2025/06/13</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -8985,12 +8985,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2025/05/13</t>
+          <t>2025/06/14</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -9003,12 +9003,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2025/05/14</t>
+          <t>2025/06/15</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -9021,12 +9021,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2025/05/15</t>
+          <t>2025/06/16</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -9039,12 +9039,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2025/05/16</t>
+          <t>2025/06/17</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -9057,12 +9057,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2025/05/17</t>
+          <t>2025/06/18</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -9075,12 +9075,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2025/05/18</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -9093,16 +9093,16 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2025/05/19</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D482" t="n">
         <v>101</v>
@@ -9111,12 +9111,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2025/05/19</t>
+          <t>2025/06/21</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -9129,16 +9129,16 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2025/05/20</t>
+          <t>2025/06/22</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D484" t="n">
         <v>101</v>
@@ -9147,12 +9147,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2025/05/20</t>
+          <t>2025/06/23</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -9165,16 +9165,16 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2025/05/21</t>
+          <t>2025/06/24</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D486" t="n">
         <v>101</v>
@@ -9183,7 +9183,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2025/05/21</t>
+          <t>2025/06/25</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D487" t="n">
         <v>101</v>
@@ -9201,7 +9201,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2025/05/22</t>
+          <t>2025/06/26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -9219,7 +9219,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2025/05/23</t>
+          <t>2025/06/27</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D489" t="n">
         <v>101</v>
@@ -9237,12 +9237,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2025/05/23</t>
+          <t>2025/06/28</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -9255,12 +9255,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2025/05/24</t>
+          <t>2025/06/29</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -9273,12 +9273,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2025/05/25</t>
+          <t>2025/06/30</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -9291,16 +9291,16 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2025/05/25</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D493" t="n">
         <v>101</v>
@@ -9309,12 +9309,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/07/02</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -9327,12 +9327,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2025/05/27</t>
+          <t>2025/07/03</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -9345,12 +9345,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2025/05/28</t>
+          <t>2025/07/04</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -9363,12 +9363,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2025/05/29</t>
+          <t>2025/07/05</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -9381,12 +9381,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2025/05/30</t>
+          <t>2025/07/06</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -9399,12 +9399,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2025/05/31</t>
+          <t>2025/07/07</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -9417,12 +9417,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2025/06/01</t>
+          <t>2025/07/08</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -9435,12 +9435,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2025/07/09</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -9453,12 +9453,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2025/06/03</t>
+          <t>2025/07/10</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -9471,12 +9471,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2025/06/04</t>
+          <t>2025/07/11</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -9489,12 +9489,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2025/06/05</t>
+          <t>2025/07/12</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -9507,12 +9507,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2025/06/06</t>
+          <t>2025/07/13</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -9525,12 +9525,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2025/06/07</t>
+          <t>2025/07/14</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -9543,16 +9543,16 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2025/06/08</t>
+          <t>2025/07/15</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D507" t="n">
         <v>101</v>
@@ -9561,12 +9561,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2025/06/08</t>
+          <t>2025/07/16</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -9579,12 +9579,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2025/06/09</t>
+          <t>2025/07/17</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -9597,12 +9597,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2025/06/10</t>
+          <t>2025/07/18</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -9615,16 +9615,16 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2025/06/10</t>
+          <t>2025/07/19</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D511" t="n">
         <v>101</v>
@@ -9633,12 +9633,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2025/06/11</t>
+          <t>2025/07/20</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -9651,12 +9651,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2025/06/12</t>
+          <t>2025/07/21</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -9669,12 +9669,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2025/06/13</t>
+          <t>2025/07/22</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -9687,12 +9687,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2025/06/14</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -9705,12 +9705,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2025/06/15</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -9723,16 +9723,16 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2025/06/16</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D517" t="n">
         <v>101</v>
@@ -9741,12 +9741,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2025/06/16</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -9759,12 +9759,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2025/06/17</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -9777,12 +9777,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2025/06/18</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -9795,16 +9795,16 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2025/06/19</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D521" t="n">
         <v>101</v>
@@ -9813,846 +9813,18 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2025/06/19</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C522" t="n">
         <v>21</v>
       </c>
       <c r="D522" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>2025/06/20</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="C523" t="n">
-        <v>21</v>
-      </c>
-      <c r="D523" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>2025/06/21</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C524" t="n">
-        <v>21</v>
-      </c>
-      <c r="D524" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>2025/06/22</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="C525" t="n">
-        <v>21</v>
-      </c>
-      <c r="D525" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>2025/06/23</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="C526" t="n">
-        <v>21</v>
-      </c>
-      <c r="D526" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="C527" t="n">
-        <v>20</v>
-      </c>
-      <c r="D527" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="C528" t="n">
-        <v>21</v>
-      </c>
-      <c r="D528" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="C529" t="n">
-        <v>20</v>
-      </c>
-      <c r="D529" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="C530" t="n">
-        <v>21</v>
-      </c>
-      <c r="D530" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>2025/06/26</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="C531" t="n">
-        <v>21</v>
-      </c>
-      <c r="D531" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>2025/06/27</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="C532" t="n">
-        <v>21</v>
-      </c>
-      <c r="D532" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>2025/06/28</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C533" t="n">
-        <v>21</v>
-      </c>
-      <c r="D533" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>2025/06/29</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="C534" t="n">
-        <v>21</v>
-      </c>
-      <c r="D534" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="C535" t="n">
-        <v>21</v>
-      </c>
-      <c r="D535" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="C536" t="n">
-        <v>21</v>
-      </c>
-      <c r="D536" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>2025/07/02</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="C537" t="n">
-        <v>21</v>
-      </c>
-      <c r="D537" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>2025/07/03</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="C538" t="n">
-        <v>21</v>
-      </c>
-      <c r="D538" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>2025/07/04</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="C539" t="n">
-        <v>21</v>
-      </c>
-      <c r="D539" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>2025/07/05</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C540" t="n">
-        <v>20</v>
-      </c>
-      <c r="D540" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>2025/07/05</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C541" t="n">
-        <v>21</v>
-      </c>
-      <c r="D541" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>2025/07/06</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="C542" t="n">
-        <v>21</v>
-      </c>
-      <c r="D542" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="C543" t="n">
-        <v>21</v>
-      </c>
-      <c r="D543" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="C544" t="n">
-        <v>21</v>
-      </c>
-      <c r="D544" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>2025/07/09</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="C545" t="n">
-        <v>21</v>
-      </c>
-      <c r="D545" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>2025/07/10</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="C546" t="n">
-        <v>21</v>
-      </c>
-      <c r="D546" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>2025/07/11</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="C547" t="n">
-        <v>21</v>
-      </c>
-      <c r="D547" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>2025/07/12</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C548" t="n">
-        <v>21</v>
-      </c>
-      <c r="D548" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>2025/07/13</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="C549" t="n">
-        <v>21</v>
-      </c>
-      <c r="D549" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>2025/07/14</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="C550" t="n">
-        <v>21</v>
-      </c>
-      <c r="D550" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>2025/07/15</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="C551" t="n">
-        <v>21</v>
-      </c>
-      <c r="D551" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>2025/07/16</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="C552" t="n">
-        <v>21</v>
-      </c>
-      <c r="D552" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>2025/07/17</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="C553" t="n">
-        <v>21</v>
-      </c>
-      <c r="D553" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>2025/07/18</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="C554" t="n">
-        <v>21</v>
-      </c>
-      <c r="D554" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>2025/07/19</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C555" t="n">
-        <v>20</v>
-      </c>
-      <c r="D555" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>2025/07/19</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C556" t="n">
-        <v>21</v>
-      </c>
-      <c r="D556" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>2025/07/20</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="C557" t="n">
-        <v>21</v>
-      </c>
-      <c r="D557" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>2025/07/21</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="C558" t="n">
-        <v>21</v>
-      </c>
-      <c r="D558" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>2025/07/22</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="C559" t="n">
-        <v>21</v>
-      </c>
-      <c r="D559" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="C560" t="n">
-        <v>21</v>
-      </c>
-      <c r="D560" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>2025/07/24</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="C561" t="n">
-        <v>21</v>
-      </c>
-      <c r="D561" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>金</t>
-        </is>
-      </c>
-      <c r="C562" t="n">
-        <v>21</v>
-      </c>
-      <c r="D562" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>2025/07/26</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>土</t>
-        </is>
-      </c>
-      <c r="C563" t="n">
-        <v>21</v>
-      </c>
-      <c r="D563" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>2025/07/27</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="C564" t="n">
-        <v>21</v>
-      </c>
-      <c r="D564" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="C565" t="n">
-        <v>21</v>
-      </c>
-      <c r="D565" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>火</t>
-        </is>
-      </c>
-      <c r="C566" t="n">
-        <v>21</v>
-      </c>
-      <c r="D566" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-      <c r="C567" t="n">
-        <v>21</v>
-      </c>
-      <c r="D567" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>2025/07/31</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>木</t>
-        </is>
-      </c>
-      <c r="C568" t="n">
-        <v>21</v>
-      </c>
-      <c r="D568" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D743"/>
+  <dimension ref="A1:D744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13701,12 +13701,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/02/28</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -13719,12 +13719,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -13737,12 +13737,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -13755,12 +13755,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -13773,12 +13773,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -13791,18 +13791,36 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>22</v>
+      </c>
+      <c r="D743" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B743" t="inlineStr">
+      <c r="B744" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C743" t="n">
-        <v>22</v>
-      </c>
-      <c r="D743" t="n">
+      <c r="C744" t="n">
+        <v>22</v>
+      </c>
+      <c r="D744" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D744"/>
+  <dimension ref="A1:D745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13719,12 +13719,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/01</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -13737,12 +13737,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -13755,12 +13755,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -13773,12 +13773,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -13791,12 +13791,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -13809,18 +13809,36 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>22</v>
+      </c>
+      <c r="D744" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B745" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C744" t="n">
-        <v>22</v>
-      </c>
-      <c r="D744" t="n">
+      <c r="C745" t="n">
+        <v>22</v>
+      </c>
+      <c r="D745" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D745"/>
+  <dimension ref="A1:D746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13737,12 +13737,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/02</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -13755,12 +13755,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -13773,12 +13773,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -13791,12 +13791,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -13809,12 +13809,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -13827,18 +13827,36 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>22</v>
+      </c>
+      <c r="D745" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B745" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C745" t="n">
-        <v>22</v>
-      </c>
-      <c r="D745" t="n">
+      <c r="C746" t="n">
+        <v>22</v>
+      </c>
+      <c r="D746" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D746"/>
+  <dimension ref="A1:D747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13755,7 +13755,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/03</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -13764,7 +13764,7 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D741" t="n">
         <v>101</v>
@@ -13773,12 +13773,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -13791,12 +13791,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -13809,12 +13809,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -13827,12 +13827,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -13845,18 +13845,36 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>22</v>
+      </c>
+      <c r="D746" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B746" t="inlineStr">
+      <c r="B747" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C746" t="n">
-        <v>22</v>
-      </c>
-      <c r="D746" t="n">
+      <c r="C747" t="n">
+        <v>22</v>
+      </c>
+      <c r="D747" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D747"/>
+  <dimension ref="A1:D748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13773,12 +13773,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/04</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -13791,12 +13791,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -13809,12 +13809,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -13827,12 +13827,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -13845,12 +13845,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -13863,18 +13863,36 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>22</v>
+      </c>
+      <c r="D747" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B747" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C747" t="n">
-        <v>22</v>
-      </c>
-      <c r="D747" t="n">
+      <c r="C748" t="n">
+        <v>22</v>
+      </c>
+      <c r="D748" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D748"/>
+  <dimension ref="A1:D749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13791,12 +13791,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/05</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -13809,12 +13809,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -13827,12 +13827,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -13845,12 +13845,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -13863,12 +13863,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C747" t="n">
@@ -13881,18 +13881,36 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>22</v>
+      </c>
+      <c r="D748" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B749" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C748" t="n">
-        <v>22</v>
-      </c>
-      <c r="D748" t="n">
+      <c r="C749" t="n">
+        <v>22</v>
+      </c>
+      <c r="D749" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D749"/>
+  <dimension ref="A1:D750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13809,12 +13809,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -13827,12 +13827,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -13845,12 +13845,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -13863,12 +13863,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C747" t="n">
@@ -13881,12 +13881,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -13899,18 +13899,36 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>22</v>
+      </c>
+      <c r="D749" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B749" t="inlineStr">
+      <c r="B750" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C749" t="n">
-        <v>22</v>
-      </c>
-      <c r="D749" t="n">
+      <c r="C750" t="n">
+        <v>22</v>
+      </c>
+      <c r="D750" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D750"/>
+  <dimension ref="A1:D751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13827,12 +13827,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/07</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -13845,12 +13845,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -13863,12 +13863,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C747" t="n">
@@ -13881,12 +13881,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -13899,12 +13899,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -13917,18 +13917,36 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>22</v>
+      </c>
+      <c r="D750" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
+      <c r="B751" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C750" t="n">
-        <v>22</v>
-      </c>
-      <c r="D750" t="n">
+      <c r="C751" t="n">
+        <v>22</v>
+      </c>
+      <c r="D751" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D751"/>
+  <dimension ref="A1:D752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13845,16 +13845,16 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/08</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C746" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D746" t="n">
         <v>101</v>
@@ -13863,12 +13863,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C747" t="n">
@@ -13881,12 +13881,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -13899,12 +13899,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -13917,12 +13917,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -13935,18 +13935,36 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>22</v>
+      </c>
+      <c r="D751" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B751" t="inlineStr">
+      <c r="B752" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C751" t="n">
-        <v>22</v>
-      </c>
-      <c r="D751" t="n">
+      <c r="C752" t="n">
+        <v>22</v>
+      </c>
+      <c r="D752" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D752"/>
+  <dimension ref="A1:D753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13863,16 +13863,16 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/09</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C747" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D747" t="n">
         <v>101</v>
@@ -13881,12 +13881,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C748" t="n">
@@ -13899,12 +13899,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -13917,12 +13917,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -13935,12 +13935,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -13953,18 +13953,36 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>22</v>
+      </c>
+      <c r="D752" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B752" t="inlineStr">
+      <c r="B753" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C752" t="n">
-        <v>22</v>
-      </c>
-      <c r="D752" t="n">
+      <c r="C753" t="n">
+        <v>22</v>
+      </c>
+      <c r="D753" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D753"/>
+  <dimension ref="A1:D754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13881,7 +13881,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/10</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -13890,7 +13890,7 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D748" t="n">
         <v>101</v>
@@ -13899,12 +13899,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -13917,12 +13917,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -13935,12 +13935,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -13953,12 +13953,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -13971,18 +13971,36 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>22</v>
+      </c>
+      <c r="D753" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B754" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C753" t="n">
-        <v>22</v>
-      </c>
-      <c r="D753" t="n">
+      <c r="C754" t="n">
+        <v>22</v>
+      </c>
+      <c r="D754" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D754"/>
+  <dimension ref="A1:D755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13899,16 +13899,16 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/11</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C749" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D749" t="n">
         <v>101</v>
@@ -13917,12 +13917,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -13935,12 +13935,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -13953,12 +13953,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -13971,12 +13971,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -13989,18 +13989,36 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>22</v>
+      </c>
+      <c r="D754" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C754" t="n">
-        <v>22</v>
-      </c>
-      <c r="D754" t="n">
+      <c r="C755" t="n">
+        <v>22</v>
+      </c>
+      <c r="D755" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D755"/>
+  <dimension ref="A1:D756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13917,16 +13917,16 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/12</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C750" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D750" t="n">
         <v>101</v>
@@ -13935,12 +13935,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -13953,12 +13953,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -13971,12 +13971,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -13989,12 +13989,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -14007,18 +14007,36 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>22</v>
+      </c>
+      <c r="D755" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B756" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C755" t="n">
-        <v>22</v>
-      </c>
-      <c r="D755" t="n">
+      <c r="C756" t="n">
+        <v>22</v>
+      </c>
+      <c r="D756" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D756"/>
+  <dimension ref="A1:D757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13935,16 +13935,16 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C751" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D751" t="n">
         <v>101</v>
@@ -13953,12 +13953,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -13971,12 +13971,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -13989,12 +13989,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -14007,12 +14007,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -14025,18 +14025,36 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>22</v>
+      </c>
+      <c r="D756" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C756" t="n">
-        <v>22</v>
-      </c>
-      <c r="D756" t="n">
+      <c r="C757" t="n">
+        <v>22</v>
+      </c>
+      <c r="D757" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D757"/>
+  <dimension ref="A1:D758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13953,16 +13953,16 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/14</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C752" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D752" t="n">
         <v>101</v>
@@ -13971,12 +13971,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -13989,12 +13989,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -14007,12 +14007,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -14025,12 +14025,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -14043,18 +14043,36 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>22</v>
+      </c>
+      <c r="D757" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C757" t="n">
-        <v>22</v>
-      </c>
-      <c r="D757" t="n">
+      <c r="C758" t="n">
+        <v>22</v>
+      </c>
+      <c r="D758" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D758"/>
+  <dimension ref="A1:D759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13971,16 +13971,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/15</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D753" t="n">
         <v>101</v>
@@ -13989,12 +13989,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -14007,12 +14007,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -14025,12 +14025,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -14043,12 +14043,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -14061,18 +14061,36 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>22</v>
+      </c>
+      <c r="D758" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B759" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C758" t="n">
-        <v>22</v>
-      </c>
-      <c r="D758" t="n">
+      <c r="C759" t="n">
+        <v>22</v>
+      </c>
+      <c r="D759" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D759"/>
+  <dimension ref="A1:D760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13989,16 +13989,16 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/16</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C754" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D754" t="n">
         <v>101</v>
@@ -14007,12 +14007,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -14025,12 +14025,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -14043,12 +14043,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -14061,12 +14061,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -14079,18 +14079,36 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>22</v>
+      </c>
+      <c r="D759" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B760" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C759" t="n">
-        <v>22</v>
-      </c>
-      <c r="D759" t="n">
+      <c r="C760" t="n">
+        <v>22</v>
+      </c>
+      <c r="D760" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D760"/>
+  <dimension ref="A1:D761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14007,7 +14007,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/17</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -14016,7 +14016,7 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D755" t="n">
         <v>101</v>
@@ -14025,12 +14025,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -14043,12 +14043,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -14061,12 +14061,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -14079,12 +14079,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C759" t="n">
@@ -14097,18 +14097,36 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>22</v>
+      </c>
+      <c r="D760" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B761" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C760" t="n">
-        <v>22</v>
-      </c>
-      <c r="D760" t="n">
+      <c r="C761" t="n">
+        <v>22</v>
+      </c>
+      <c r="D761" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D761"/>
+  <dimension ref="A1:D762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14025,16 +14025,16 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/18</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C756" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D756" t="n">
         <v>101</v>
@@ -14043,12 +14043,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C757" t="n">
@@ -14061,12 +14061,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -14079,12 +14079,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C759" t="n">
@@ -14097,12 +14097,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -14115,18 +14115,36 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>22</v>
+      </c>
+      <c r="D761" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B762" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C761" t="n">
-        <v>22</v>
-      </c>
-      <c r="D761" t="n">
+      <c r="C762" t="n">
+        <v>22</v>
+      </c>
+      <c r="D762" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D762"/>
+  <dimension ref="A1:D763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14043,16 +14043,16 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/19</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D757" t="n">
         <v>101</v>
@@ -14061,12 +14061,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C758" t="n">
@@ -14079,12 +14079,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C759" t="n">
@@ -14097,12 +14097,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -14115,12 +14115,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -14133,18 +14133,36 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>22</v>
+      </c>
+      <c r="D762" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
+      <c r="B763" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C762" t="n">
-        <v>22</v>
-      </c>
-      <c r="D762" t="n">
+      <c r="C763" t="n">
+        <v>22</v>
+      </c>
+      <c r="D763" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D763"/>
+  <dimension ref="A1:D764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14061,16 +14061,16 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/20</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C758" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D758" t="n">
         <v>101</v>
@@ -14079,12 +14079,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C759" t="n">
@@ -14097,12 +14097,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -14115,12 +14115,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -14133,12 +14133,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C762" t="n">
@@ -14151,18 +14151,36 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>22</v>
+      </c>
+      <c r="D763" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
+      <c r="B764" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C763" t="n">
-        <v>22</v>
-      </c>
-      <c r="D763" t="n">
+      <c r="C764" t="n">
+        <v>22</v>
+      </c>
+      <c r="D764" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D764"/>
+  <dimension ref="A1:D765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14079,16 +14079,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D759" t="n">
         <v>101</v>
@@ -14097,12 +14097,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -14115,12 +14115,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -14133,12 +14133,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C762" t="n">
@@ -14151,12 +14151,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -14169,18 +14169,36 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>22</v>
+      </c>
+      <c r="D764" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
+      <c r="B765" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C764" t="n">
-        <v>22</v>
-      </c>
-      <c r="D764" t="n">
+      <c r="C765" t="n">
+        <v>22</v>
+      </c>
+      <c r="D765" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D765"/>
+  <dimension ref="A1:D766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14097,16 +14097,16 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/22</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C760" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D760" t="n">
         <v>101</v>
@@ -14115,12 +14115,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -14133,12 +14133,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C762" t="n">
@@ -14151,12 +14151,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -14169,12 +14169,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -14187,18 +14187,36 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>22</v>
+      </c>
+      <c r="D765" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B766" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C765" t="n">
-        <v>22</v>
-      </c>
-      <c r="D765" t="n">
+      <c r="C766" t="n">
+        <v>22</v>
+      </c>
+      <c r="D766" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D766"/>
+  <dimension ref="A1:D767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14115,16 +14115,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/23</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D761" t="n">
         <v>101</v>
@@ -14133,12 +14133,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C762" t="n">
@@ -14151,12 +14151,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -14169,12 +14169,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -14187,12 +14187,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -14205,18 +14205,36 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>22</v>
+      </c>
+      <c r="D766" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
+      <c r="B767" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C766" t="n">
-        <v>22</v>
-      </c>
-      <c r="D766" t="n">
+      <c r="C767" t="n">
+        <v>22</v>
+      </c>
+      <c r="D767" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D767"/>
+  <dimension ref="A1:D768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14133,7 +14133,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/24</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D762" t="n">
         <v>101</v>
@@ -14151,12 +14151,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -14169,12 +14169,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -14187,12 +14187,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -14205,12 +14205,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -14223,18 +14223,36 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>22</v>
+      </c>
+      <c r="D767" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
+      <c r="B768" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C767" t="n">
-        <v>22</v>
-      </c>
-      <c r="D767" t="n">
+      <c r="C768" t="n">
+        <v>22</v>
+      </c>
+      <c r="D768" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D768"/>
+  <dimension ref="A1:D769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14151,16 +14151,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/25</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D763" t="n">
         <v>101</v>
@@ -14169,12 +14169,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -14187,12 +14187,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -14205,12 +14205,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -14223,12 +14223,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -14241,18 +14241,36 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>22</v>
+      </c>
+      <c r="D768" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C768" t="n">
-        <v>22</v>
-      </c>
-      <c r="D768" t="n">
+      <c r="C769" t="n">
+        <v>22</v>
+      </c>
+      <c r="D769" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D769"/>
+  <dimension ref="A1:D771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14169,16 +14169,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/26</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D764" t="n">
         <v>101</v>
@@ -14187,16 +14187,16 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/03/27</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C765" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D765" t="n">
         <v>101</v>
@@ -14205,12 +14205,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -14223,12 +14223,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -14241,12 +14241,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C768" t="n">
@@ -14259,18 +14259,54 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
+          <t>2027/01/01</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>22</v>
+      </c>
+      <c r="D769" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>22</v>
+      </c>
+      <c r="D770" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B771" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C769" t="n">
-        <v>22</v>
-      </c>
-      <c r="D769" t="n">
+      <c r="C771" t="n">
+        <v>22</v>
+      </c>
+      <c r="D771" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D771"/>
+  <dimension ref="A1:D772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14205,16 +14205,16 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/27</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C766" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D766" t="n">
         <v>101</v>
@@ -14223,12 +14223,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -14241,12 +14241,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C768" t="n">
@@ -14259,12 +14259,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C769" t="n">
@@ -14277,12 +14277,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -14295,18 +14295,36 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>22</v>
+      </c>
+      <c r="D771" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C771" t="n">
-        <v>22</v>
-      </c>
-      <c r="D771" t="n">
+      <c r="C772" t="n">
+        <v>22</v>
+      </c>
+      <c r="D772" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D772"/>
+  <dimension ref="A1:D773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14223,16 +14223,16 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/27</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C767" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D767" t="n">
         <v>101</v>
@@ -14241,12 +14241,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C768" t="n">
@@ -14259,12 +14259,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C769" t="n">
@@ -14277,12 +14277,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -14295,12 +14295,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -14313,18 +14313,36 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>22</v>
+      </c>
+      <c r="D772" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C772" t="n">
-        <v>22</v>
-      </c>
-      <c r="D772" t="n">
+      <c r="C773" t="n">
+        <v>22</v>
+      </c>
+      <c r="D773" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D773"/>
+  <dimension ref="A1:D774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14241,16 +14241,16 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/28</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D768" t="n">
         <v>101</v>
@@ -14259,12 +14259,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C769" t="n">
@@ -14277,12 +14277,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -14295,12 +14295,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -14313,12 +14313,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -14331,18 +14331,36 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>22</v>
+      </c>
+      <c r="D773" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
+      <c r="B774" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C773" t="n">
-        <v>22</v>
-      </c>
-      <c r="D773" t="n">
+      <c r="C774" t="n">
+        <v>22</v>
+      </c>
+      <c r="D774" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D774"/>
+  <dimension ref="A1:D775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14259,16 +14259,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/03/29</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D769" t="n">
         <v>101</v>
@@ -14277,12 +14277,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -14295,12 +14295,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -14313,12 +14313,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -14331,12 +14331,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -14349,18 +14349,36 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>22</v>
+      </c>
+      <c r="D774" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
+      <c r="B775" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C774" t="n">
-        <v>22</v>
-      </c>
-      <c r="D774" t="n">
+      <c r="C775" t="n">
+        <v>22</v>
+      </c>
+      <c r="D775" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D775"/>
+  <dimension ref="A1:D776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14277,7 +14277,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -14286,7 +14286,7 @@
         </is>
       </c>
       <c r="C770" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D770" t="n">
         <v>101</v>
@@ -14295,12 +14295,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -14313,12 +14313,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -14331,12 +14331,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -14349,12 +14349,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -14367,18 +14367,36 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>22</v>
+      </c>
+      <c r="D775" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B776" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C775" t="n">
-        <v>22</v>
-      </c>
-      <c r="D775" t="n">
+      <c r="C776" t="n">
+        <v>22</v>
+      </c>
+      <c r="D776" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D776"/>
+  <dimension ref="A1:D777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14295,7 +14295,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -14304,7 +14304,7 @@
         </is>
       </c>
       <c r="C771" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D771" t="n">
         <v>101</v>
@@ -14313,12 +14313,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -14331,12 +14331,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -14349,12 +14349,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -14367,12 +14367,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -14385,18 +14385,36 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>22</v>
+      </c>
+      <c r="D776" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
+      <c r="B777" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C776" t="n">
-        <v>22</v>
-      </c>
-      <c r="D776" t="n">
+      <c r="C777" t="n">
+        <v>22</v>
+      </c>
+      <c r="D777" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D777"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14313,16 +14313,16 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C772" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D772" t="n">
         <v>101</v>
@@ -14331,12 +14331,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -14349,12 +14349,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -14367,12 +14367,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -14385,12 +14385,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C776" t="n">
@@ -14403,18 +14403,36 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>22</v>
+      </c>
+      <c r="D777" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
+      <c r="B778" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C777" t="n">
-        <v>22</v>
-      </c>
-      <c r="D777" t="n">
+      <c r="C778" t="n">
+        <v>22</v>
+      </c>
+      <c r="D778" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D778"/>
+  <dimension ref="A1:D779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14331,12 +14331,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -14349,12 +14349,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -14367,12 +14367,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -14385,12 +14385,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C776" t="n">
@@ -14403,12 +14403,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -14421,18 +14421,36 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>22</v>
+      </c>
+      <c r="D778" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
+      <c r="B779" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C778" t="n">
-        <v>22</v>
-      </c>
-      <c r="D778" t="n">
+      <c r="C779" t="n">
+        <v>22</v>
+      </c>
+      <c r="D779" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14349,16 +14349,16 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C774" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D774" t="n">
         <v>101</v>
@@ -14367,12 +14367,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -14385,12 +14385,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C776" t="n">
@@ -14403,12 +14403,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -14421,12 +14421,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -14439,18 +14439,36 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>22</v>
+      </c>
+      <c r="D779" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C779" t="n">
-        <v>22</v>
-      </c>
-      <c r="D779" t="n">
+      <c r="C780" t="n">
+        <v>22</v>
+      </c>
+      <c r="D780" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D780"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14367,16 +14367,16 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C775" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D775" t="n">
         <v>101</v>
@@ -14385,12 +14385,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C776" t="n">
@@ -14403,12 +14403,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -14421,12 +14421,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -14439,12 +14439,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -14457,18 +14457,36 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>22</v>
+      </c>
+      <c r="D780" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
+      <c r="B781" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C780" t="n">
-        <v>22</v>
-      </c>
-      <c r="D780" t="n">
+      <c r="C781" t="n">
+        <v>22</v>
+      </c>
+      <c r="D781" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14385,16 +14385,16 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/19</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C776" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D776" t="n">
         <v>101</v>
@@ -14403,12 +14403,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -14421,12 +14421,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -14439,12 +14439,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -14457,12 +14457,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -14475,18 +14475,36 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>22</v>
+      </c>
+      <c r="D781" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C781" t="n">
-        <v>22</v>
-      </c>
-      <c r="D781" t="n">
+      <c r="C782" t="n">
+        <v>22</v>
+      </c>
+      <c r="D782" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D782"/>
+  <dimension ref="A1:D783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14403,16 +14403,16 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C777" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D777" t="n">
         <v>101</v>
@@ -14421,12 +14421,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -14439,12 +14439,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -14457,12 +14457,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -14475,12 +14475,12 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -14493,18 +14493,36 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>22</v>
+      </c>
+      <c r="D782" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B783" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C782" t="n">
-        <v>22</v>
-      </c>
-      <c r="D782" t="n">
+      <c r="C783" t="n">
+        <v>22</v>
+      </c>
+      <c r="D783" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D783"/>
+  <dimension ref="A1:D784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14421,7 +14421,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D778" t="n">
         <v>101</v>
@@ -14439,12 +14439,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -14457,12 +14457,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -14475,12 +14475,12 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -14493,12 +14493,12 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -14511,18 +14511,36 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>22</v>
+      </c>
+      <c r="D783" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B784" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C783" t="n">
-        <v>22</v>
-      </c>
-      <c r="D783" t="n">
+      <c r="C784" t="n">
+        <v>22</v>
+      </c>
+      <c r="D784" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D784"/>
+  <dimension ref="A1:D785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14439,16 +14439,16 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C779" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D779" t="n">
         <v>101</v>
@@ -14457,12 +14457,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -14475,12 +14475,12 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -14493,12 +14493,12 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -14511,12 +14511,12 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -14529,18 +14529,36 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>22</v>
+      </c>
+      <c r="D784" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
+      <c r="B785" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C784" t="n">
-        <v>22</v>
-      </c>
-      <c r="D784" t="n">
+      <c r="C785" t="n">
+        <v>22</v>
+      </c>
+      <c r="D785" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D785"/>
+  <dimension ref="A1:D786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14457,16 +14457,16 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C780" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D780" t="n">
         <v>101</v>
@@ -14475,12 +14475,12 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -14493,12 +14493,12 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -14511,12 +14511,12 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -14529,12 +14529,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -14547,18 +14547,36 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>22</v>
+      </c>
+      <c r="D785" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C785" t="n">
-        <v>22</v>
-      </c>
-      <c r="D785" t="n">
+      <c r="C786" t="n">
+        <v>22</v>
+      </c>
+      <c r="D786" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D786"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14475,16 +14475,16 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D781" t="n">
         <v>101</v>
@@ -14493,12 +14493,12 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -14511,12 +14511,12 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -14529,12 +14529,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -14547,12 +14547,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -14565,18 +14565,36 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>22</v>
+      </c>
+      <c r="D786" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B787" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C786" t="n">
-        <v>22</v>
-      </c>
-      <c r="D786" t="n">
+      <c r="C787" t="n">
+        <v>22</v>
+      </c>
+      <c r="D787" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14493,16 +14493,16 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D782" t="n">
         <v>101</v>
@@ -14511,12 +14511,12 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -14529,12 +14529,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -14547,12 +14547,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -14565,12 +14565,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -14583,18 +14583,36 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>22</v>
+      </c>
+      <c r="D787" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C787" t="n">
-        <v>22</v>
-      </c>
-      <c r="D787" t="n">
+      <c r="C788" t="n">
+        <v>22</v>
+      </c>
+      <c r="D788" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D788"/>
+  <dimension ref="A1:D789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14511,16 +14511,16 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D783" t="n">
         <v>101</v>
@@ -14529,12 +14529,12 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -14547,12 +14547,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -14565,12 +14565,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -14583,12 +14583,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -14601,18 +14601,36 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>22</v>
+      </c>
+      <c r="D788" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
+      <c r="B789" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C788" t="n">
-        <v>22</v>
-      </c>
-      <c r="D788" t="n">
+      <c r="C789" t="n">
+        <v>22</v>
+      </c>
+      <c r="D789" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D789"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14529,16 +14529,16 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C784" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D784" t="n">
         <v>101</v>
@@ -14547,12 +14547,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C785" t="n">
@@ -14565,12 +14565,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -14583,12 +14583,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -14601,12 +14601,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -14619,18 +14619,36 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>22</v>
+      </c>
+      <c r="D789" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
+      <c r="B790" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C789" t="n">
-        <v>22</v>
-      </c>
-      <c r="D789" t="n">
+      <c r="C790" t="n">
+        <v>22</v>
+      </c>
+      <c r="D790" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14547,7 +14547,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/28</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -14565,12 +14565,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -14583,12 +14583,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -14601,12 +14601,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -14619,12 +14619,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -14637,18 +14637,36 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>22</v>
+      </c>
+      <c r="D790" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
+      <c r="B791" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C790" t="n">
-        <v>22</v>
-      </c>
-      <c r="D790" t="n">
+      <c r="C791" t="n">
+        <v>22</v>
+      </c>
+      <c r="D791" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D791"/>
+  <dimension ref="A1:D792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14565,16 +14565,16 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D786" t="n">
         <v>101</v>
@@ -14583,12 +14583,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -14601,12 +14601,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -14619,12 +14619,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -14637,12 +14637,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -14655,18 +14655,36 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>22</v>
+      </c>
+      <c r="D791" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
+      <c r="B792" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C791" t="n">
-        <v>22</v>
-      </c>
-      <c r="D791" t="n">
+      <c r="C792" t="n">
+        <v>22</v>
+      </c>
+      <c r="D792" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14583,16 +14583,16 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D787" t="n">
         <v>101</v>
@@ -14601,12 +14601,12 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -14619,12 +14619,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -14637,12 +14637,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -14655,12 +14655,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -14673,18 +14673,36 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>22</v>
+      </c>
+      <c r="D792" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
+      <c r="B793" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C792" t="n">
-        <v>22</v>
-      </c>
-      <c r="D792" t="n">
+      <c r="C793" t="n">
+        <v>22</v>
+      </c>
+      <c r="D793" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14601,16 +14601,16 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C788" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D788" t="n">
         <v>101</v>
@@ -14619,12 +14619,12 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -14637,12 +14637,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -14655,12 +14655,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -14673,12 +14673,12 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -14691,18 +14691,36 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>22</v>
+      </c>
+      <c r="D793" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
+      <c r="B794" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C793" t="n">
-        <v>22</v>
-      </c>
-      <c r="D793" t="n">
+      <c r="C794" t="n">
+        <v>22</v>
+      </c>
+      <c r="D794" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D794"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14619,16 +14619,16 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/01</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C789" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D789" t="n">
         <v>101</v>
@@ -14637,12 +14637,12 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -14655,12 +14655,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -14673,12 +14673,12 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -14691,12 +14691,12 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -14709,18 +14709,36 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>22</v>
+      </c>
+      <c r="D794" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
+      <c r="B795" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C794" t="n">
-        <v>22</v>
-      </c>
-      <c r="D794" t="n">
+      <c r="C795" t="n">
+        <v>22</v>
+      </c>
+      <c r="D795" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14637,16 +14637,16 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/02</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C790" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D790" t="n">
         <v>101</v>
@@ -14655,12 +14655,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C791" t="n">
@@ -14673,12 +14673,12 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -14691,12 +14691,12 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -14709,12 +14709,12 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -14727,18 +14727,36 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>22</v>
+      </c>
+      <c r="D795" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
+      <c r="B796" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C795" t="n">
-        <v>22</v>
-      </c>
-      <c r="D795" t="n">
+      <c r="C796" t="n">
+        <v>22</v>
+      </c>
+      <c r="D796" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D796"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14655,16 +14655,16 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C791" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D791" t="n">
         <v>101</v>
@@ -14673,12 +14673,12 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -14691,12 +14691,12 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -14709,12 +14709,12 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -14727,12 +14727,12 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -14745,18 +14745,36 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>22</v>
+      </c>
+      <c r="D796" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
+      <c r="B797" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C796" t="n">
-        <v>22</v>
-      </c>
-      <c r="D796" t="n">
+      <c r="C797" t="n">
+        <v>22</v>
+      </c>
+      <c r="D797" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14673,7 +14673,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -14682,7 +14682,7 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D792" t="n">
         <v>101</v>
@@ -14691,12 +14691,12 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -14709,12 +14709,12 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -14727,12 +14727,12 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -14745,12 +14745,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -14763,18 +14763,36 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>22</v>
+      </c>
+      <c r="D797" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
+      <c r="B798" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C797" t="n">
-        <v>22</v>
-      </c>
-      <c r="D797" t="n">
+      <c r="C798" t="n">
+        <v>22</v>
+      </c>
+      <c r="D798" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D798"/>
+  <dimension ref="A1:D799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14691,16 +14691,16 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C793" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D793" t="n">
         <v>101</v>
@@ -14709,12 +14709,12 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -14727,12 +14727,12 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -14745,12 +14745,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -14763,12 +14763,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -14781,18 +14781,36 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>22</v>
+      </c>
+      <c r="D798" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
+      <c r="B799" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C798" t="n">
-        <v>22</v>
-      </c>
-      <c r="D798" t="n">
+      <c r="C799" t="n">
+        <v>22</v>
+      </c>
+      <c r="D799" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D799"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14709,16 +14709,16 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C794" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D794" t="n">
         <v>101</v>
@@ -14727,12 +14727,12 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -14745,12 +14745,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -14763,12 +14763,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -14781,12 +14781,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -14799,18 +14799,36 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>22</v>
+      </c>
+      <c r="D799" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
+      <c r="B800" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C799" t="n">
-        <v>22</v>
-      </c>
-      <c r="D799" t="n">
+      <c r="C800" t="n">
+        <v>22</v>
+      </c>
+      <c r="D800" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14727,16 +14727,16 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C795" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D795" t="n">
         <v>101</v>
@@ -14745,12 +14745,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -14763,12 +14763,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -14781,12 +14781,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -14799,12 +14799,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -14817,18 +14817,36 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>22</v>
+      </c>
+      <c r="D800" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
+      <c r="B801" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C800" t="n">
-        <v>22</v>
-      </c>
-      <c r="D800" t="n">
+      <c r="C801" t="n">
+        <v>22</v>
+      </c>
+      <c r="D801" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D801"/>
+  <dimension ref="A1:D802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14745,16 +14745,16 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/08</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C796" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D796" t="n">
         <v>101</v>
@@ -14763,12 +14763,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -14781,12 +14781,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -14799,12 +14799,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -14817,12 +14817,12 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -14835,18 +14835,36 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>22</v>
+      </c>
+      <c r="D801" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
+      <c r="B802" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C801" t="n">
-        <v>22</v>
-      </c>
-      <c r="D801" t="n">
+      <c r="C802" t="n">
+        <v>22</v>
+      </c>
+      <c r="D802" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D802"/>
+  <dimension ref="A1:D803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14763,16 +14763,16 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/09</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C797" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D797" t="n">
         <v>101</v>
@@ -14781,12 +14781,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -14799,12 +14799,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -14817,12 +14817,12 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -14835,12 +14835,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -14853,18 +14853,36 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>22</v>
+      </c>
+      <c r="D802" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
+      <c r="B803" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C802" t="n">
-        <v>22</v>
-      </c>
-      <c r="D802" t="n">
+      <c r="C803" t="n">
+        <v>22</v>
+      </c>
+      <c r="D803" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D803"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14781,16 +14781,16 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/10</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C798" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D798" t="n">
         <v>101</v>
@@ -14799,12 +14799,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -14817,12 +14817,12 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -14835,12 +14835,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -14853,12 +14853,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -14871,18 +14871,36 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>22</v>
+      </c>
+      <c r="D803" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
+      <c r="B804" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C803" t="n">
-        <v>22</v>
-      </c>
-      <c r="D803" t="n">
+      <c r="C804" t="n">
+        <v>22</v>
+      </c>
+      <c r="D804" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14799,7 +14799,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/11</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="C799" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D799" t="n">
         <v>101</v>
@@ -14817,12 +14817,12 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -14835,12 +14835,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -14853,12 +14853,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -14871,12 +14871,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -14889,18 +14889,36 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>22</v>
+      </c>
+      <c r="D804" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
+      <c r="B805" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C804" t="n">
-        <v>22</v>
-      </c>
-      <c r="D804" t="n">
+      <c r="C805" t="n">
+        <v>22</v>
+      </c>
+      <c r="D805" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D805"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14817,16 +14817,16 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C800" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D800" t="n">
         <v>101</v>
@@ -14835,12 +14835,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -14853,12 +14853,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -14871,12 +14871,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -14889,12 +14889,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -14907,18 +14907,36 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>22</v>
+      </c>
+      <c r="D805" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B805" t="inlineStr">
+      <c r="B806" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C805" t="n">
-        <v>22</v>
-      </c>
-      <c r="D805" t="n">
+      <c r="C806" t="n">
+        <v>22</v>
+      </c>
+      <c r="D806" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14835,16 +14835,16 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/13</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C801" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D801" t="n">
         <v>101</v>
@@ -14853,12 +14853,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -14871,12 +14871,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -14889,12 +14889,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -14907,12 +14907,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -14925,18 +14925,36 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>22</v>
+      </c>
+      <c r="D806" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
+      <c r="B807" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C806" t="n">
-        <v>22</v>
-      </c>
-      <c r="D806" t="n">
+      <c r="C807" t="n">
+        <v>22</v>
+      </c>
+      <c r="D807" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14853,16 +14853,16 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C802" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D802" t="n">
         <v>101</v>
@@ -14871,12 +14871,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -14889,12 +14889,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -14907,12 +14907,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -14925,12 +14925,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -14943,18 +14943,36 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>22</v>
+      </c>
+      <c r="D807" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
+      <c r="B808" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C807" t="n">
-        <v>22</v>
-      </c>
-      <c r="D807" t="n">
+      <c r="C808" t="n">
+        <v>22</v>
+      </c>
+      <c r="D808" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D808"/>
+  <dimension ref="A1:D809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14871,16 +14871,16 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/15</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C803" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D803" t="n">
         <v>101</v>
@@ -14889,12 +14889,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -14907,12 +14907,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -14925,12 +14925,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -14943,12 +14943,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -14961,18 +14961,36 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>22</v>
+      </c>
+      <c r="D808" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B808" t="inlineStr">
+      <c r="B809" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C808" t="n">
-        <v>22</v>
-      </c>
-      <c r="D808" t="n">
+      <c r="C809" t="n">
+        <v>22</v>
+      </c>
+      <c r="D809" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D809"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14889,16 +14889,16 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/16</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C804" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D804" t="n">
         <v>101</v>
@@ -14907,12 +14907,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -14925,12 +14925,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -14943,12 +14943,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -14961,12 +14961,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -14979,18 +14979,36 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>22</v>
+      </c>
+      <c r="D809" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B809" t="inlineStr">
+      <c r="B810" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C809" t="n">
-        <v>22</v>
-      </c>
-      <c r="D809" t="n">
+      <c r="C810" t="n">
+        <v>22</v>
+      </c>
+      <c r="D810" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14907,16 +14907,16 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C805" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D805" t="n">
         <v>101</v>
@@ -14925,12 +14925,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -14943,12 +14943,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -14961,12 +14961,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -14979,12 +14979,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C809" t="n">
@@ -14997,18 +14997,36 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>22</v>
+      </c>
+      <c r="D810" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B810" t="inlineStr">
+      <c r="B811" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C810" t="n">
-        <v>22</v>
-      </c>
-      <c r="D810" t="n">
+      <c r="C811" t="n">
+        <v>22</v>
+      </c>
+      <c r="D811" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14925,7 +14925,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -14934,7 +14934,7 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D806" t="n">
         <v>101</v>
@@ -14943,12 +14943,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -14961,12 +14961,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -14979,12 +14979,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C809" t="n">
@@ -14997,12 +14997,12 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -15015,18 +15015,36 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>22</v>
+      </c>
+      <c r="D811" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B811" t="inlineStr">
+      <c r="B812" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C811" t="n">
-        <v>22</v>
-      </c>
-      <c r="D811" t="n">
+      <c r="C812" t="n">
+        <v>22</v>
+      </c>
+      <c r="D812" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D812"/>
+  <dimension ref="A1:D813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14943,16 +14943,16 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C807" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D807" t="n">
         <v>101</v>
@@ -14961,12 +14961,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -14979,12 +14979,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C809" t="n">
@@ -14997,12 +14997,12 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -15015,12 +15015,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -15033,18 +15033,36 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>22</v>
+      </c>
+      <c r="D812" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B812" t="inlineStr">
+      <c r="B813" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C812" t="n">
-        <v>22</v>
-      </c>
-      <c r="D812" t="n">
+      <c r="C813" t="n">
+        <v>22</v>
+      </c>
+      <c r="D813" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D813"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14961,16 +14961,16 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/20</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C808" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D808" t="n">
         <v>101</v>
@@ -14979,12 +14979,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C809" t="n">
@@ -14997,12 +14997,12 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -15015,12 +15015,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -15033,12 +15033,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -15051,18 +15051,36 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>22</v>
+      </c>
+      <c r="D813" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B813" t="inlineStr">
+      <c r="B814" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C813" t="n">
-        <v>22</v>
-      </c>
-      <c r="D813" t="n">
+      <c r="C814" t="n">
+        <v>22</v>
+      </c>
+      <c r="D814" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D814"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14979,16 +14979,16 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C809" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D809" t="n">
         <v>101</v>
@@ -14997,12 +14997,12 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C810" t="n">
@@ -15015,12 +15015,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -15033,12 +15033,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -15051,12 +15051,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -15069,18 +15069,36 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>22</v>
+      </c>
+      <c r="D814" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B814" t="inlineStr">
+      <c r="B815" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C814" t="n">
-        <v>22</v>
-      </c>
-      <c r="D814" t="n">
+      <c r="C815" t="n">
+        <v>22</v>
+      </c>
+      <c r="D815" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D815"/>
+  <dimension ref="A1:D816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14997,16 +14997,16 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/22</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C810" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D810" t="n">
         <v>101</v>
@@ -15015,12 +15015,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -15033,12 +15033,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -15051,12 +15051,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -15069,12 +15069,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -15087,18 +15087,36 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>22</v>
+      </c>
+      <c r="D815" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B815" t="inlineStr">
+      <c r="B816" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C815" t="n">
-        <v>22</v>
-      </c>
-      <c r="D815" t="n">
+      <c r="C816" t="n">
+        <v>22</v>
+      </c>
+      <c r="D816" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D816"/>
+  <dimension ref="A1:D817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15015,16 +15015,16 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/23</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C811" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D811" t="n">
         <v>101</v>
@@ -15033,12 +15033,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -15051,12 +15051,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -15069,12 +15069,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -15087,12 +15087,12 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -15105,18 +15105,36 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>22</v>
+      </c>
+      <c r="D816" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B816" t="inlineStr">
+      <c r="B817" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C816" t="n">
-        <v>22</v>
-      </c>
-      <c r="D816" t="n">
+      <c r="C817" t="n">
+        <v>22</v>
+      </c>
+      <c r="D817" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D817"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15033,16 +15033,16 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/24</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C812" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D812" t="n">
         <v>101</v>
@@ -15051,12 +15051,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -15069,12 +15069,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -15087,12 +15087,12 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -15105,12 +15105,12 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -15123,18 +15123,36 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>22</v>
+      </c>
+      <c r="D817" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B817" t="inlineStr">
+      <c r="B818" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C817" t="n">
-        <v>22</v>
-      </c>
-      <c r="D817" t="n">
+      <c r="C818" t="n">
+        <v>22</v>
+      </c>
+      <c r="D818" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15051,7 +15051,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/25</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="C813" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D813" t="n">
         <v>101</v>
@@ -15069,12 +15069,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -15087,12 +15087,12 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -15105,12 +15105,12 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -15123,12 +15123,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -15141,18 +15141,36 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>22</v>
+      </c>
+      <c r="D818" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B818" t="inlineStr">
+      <c r="B819" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C818" t="n">
-        <v>22</v>
-      </c>
-      <c r="D818" t="n">
+      <c r="C819" t="n">
+        <v>22</v>
+      </c>
+      <c r="D819" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D819"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15069,16 +15069,16 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/26</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C814" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D814" t="n">
         <v>101</v>
@@ -15087,12 +15087,12 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -15105,12 +15105,12 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -15123,12 +15123,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -15141,12 +15141,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -15159,18 +15159,36 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>22</v>
+      </c>
+      <c r="D819" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B819" t="inlineStr">
+      <c r="B820" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C819" t="n">
-        <v>22</v>
-      </c>
-      <c r="D819" t="n">
+      <c r="C820" t="n">
+        <v>22</v>
+      </c>
+      <c r="D820" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D820"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15087,16 +15087,16 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/27</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C815" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D815" t="n">
         <v>101</v>
@@ -15105,12 +15105,12 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -15123,12 +15123,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -15141,12 +15141,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -15159,12 +15159,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C819" t="n">
@@ -15177,18 +15177,36 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>22</v>
+      </c>
+      <c r="D820" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B820" t="inlineStr">
+      <c r="B821" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C820" t="n">
-        <v>22</v>
-      </c>
-      <c r="D820" t="n">
+      <c r="C821" t="n">
+        <v>22</v>
+      </c>
+      <c r="D821" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D821"/>
+  <dimension ref="A1:D822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15105,16 +15105,16 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/28</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C816" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D816" t="n">
         <v>101</v>
@@ -15123,12 +15123,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C817" t="n">
@@ -15141,12 +15141,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -15159,12 +15159,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C819" t="n">
@@ -15177,12 +15177,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -15195,18 +15195,36 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>22</v>
+      </c>
+      <c r="D821" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B821" t="inlineStr">
+      <c r="B822" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C821" t="n">
-        <v>22</v>
-      </c>
-      <c r="D821" t="n">
+      <c r="C822" t="n">
+        <v>22</v>
+      </c>
+      <c r="D822" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D823"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15123,16 +15123,16 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/29</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C817" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D817" t="n">
         <v>101</v>
@@ -15141,12 +15141,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -15159,12 +15159,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C819" t="n">
@@ -15177,12 +15177,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -15195,12 +15195,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -15213,18 +15213,36 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>22</v>
+      </c>
+      <c r="D822" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B822" t="inlineStr">
+      <c r="B823" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C822" t="n">
-        <v>22</v>
-      </c>
-      <c r="D822" t="n">
+      <c r="C823" t="n">
+        <v>22</v>
+      </c>
+      <c r="D823" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D823"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15141,16 +15141,16 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C818" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D818" t="n">
         <v>101</v>
@@ -15159,12 +15159,12 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C819" t="n">
@@ -15177,12 +15177,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -15195,12 +15195,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -15213,12 +15213,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -15231,18 +15231,36 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>22</v>
+      </c>
+      <c r="D823" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B823" t="inlineStr">
+      <c r="B824" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C823" t="n">
-        <v>22</v>
-      </c>
-      <c r="D823" t="n">
+      <c r="C824" t="n">
+        <v>22</v>
+      </c>
+      <c r="D824" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D824"/>
+  <dimension ref="A1:D825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15159,16 +15159,16 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C819" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D819" t="n">
         <v>101</v>
@@ -15177,12 +15177,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -15195,12 +15195,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -15213,12 +15213,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -15231,12 +15231,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -15249,18 +15249,36 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>22</v>
+      </c>
+      <c r="D824" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B824" t="inlineStr">
+      <c r="B825" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C824" t="n">
-        <v>22</v>
-      </c>
-      <c r="D824" t="n">
+      <c r="C825" t="n">
+        <v>22</v>
+      </c>
+      <c r="D825" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D825"/>
+  <dimension ref="A1:D826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15177,7 +15177,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/01</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -15186,7 +15186,7 @@
         </is>
       </c>
       <c r="C820" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D820" t="n">
         <v>101</v>
@@ -15195,12 +15195,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -15213,12 +15213,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -15231,12 +15231,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -15249,12 +15249,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -15267,18 +15267,36 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>22</v>
+      </c>
+      <c r="D825" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B825" t="inlineStr">
+      <c r="B826" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C825" t="n">
-        <v>22</v>
-      </c>
-      <c r="D825" t="n">
+      <c r="C826" t="n">
+        <v>22</v>
+      </c>
+      <c r="D826" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D826"/>
+  <dimension ref="A1:D827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15195,16 +15195,16 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/02</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C821" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D821" t="n">
         <v>101</v>
@@ -15213,12 +15213,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -15231,12 +15231,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -15249,12 +15249,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -15267,12 +15267,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -15285,18 +15285,36 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>22</v>
+      </c>
+      <c r="D826" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B826" t="inlineStr">
+      <c r="B827" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C826" t="n">
-        <v>22</v>
-      </c>
-      <c r="D826" t="n">
+      <c r="C827" t="n">
+        <v>22</v>
+      </c>
+      <c r="D827" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D827"/>
+  <dimension ref="A1:D828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15213,16 +15213,16 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/03</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C822" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D822" t="n">
         <v>101</v>
@@ -15231,12 +15231,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -15249,12 +15249,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -15267,12 +15267,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -15285,12 +15285,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -15303,18 +15303,36 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>22</v>
+      </c>
+      <c r="D827" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B827" t="inlineStr">
+      <c r="B828" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C827" t="n">
-        <v>22</v>
-      </c>
-      <c r="D827" t="n">
+      <c r="C828" t="n">
+        <v>22</v>
+      </c>
+      <c r="D828" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D828"/>
+  <dimension ref="A1:D829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15231,16 +15231,16 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/04</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C823" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D823" t="n">
         <v>101</v>
@@ -15249,12 +15249,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -15267,12 +15267,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -15285,12 +15285,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -15303,12 +15303,12 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -15321,18 +15321,36 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>22</v>
+      </c>
+      <c r="D828" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B828" t="inlineStr">
+      <c r="B829" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C828" t="n">
-        <v>22</v>
-      </c>
-      <c r="D828" t="n">
+      <c r="C829" t="n">
+        <v>22</v>
+      </c>
+      <c r="D829" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D829"/>
+  <dimension ref="A1:D830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15249,16 +15249,16 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/05</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C824" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D824" t="n">
         <v>101</v>
@@ -15267,12 +15267,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -15285,12 +15285,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -15303,12 +15303,12 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -15321,12 +15321,12 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -15339,18 +15339,36 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>22</v>
+      </c>
+      <c r="D829" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B829" t="inlineStr">
+      <c r="B830" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C829" t="n">
-        <v>22</v>
-      </c>
-      <c r="D829" t="n">
+      <c r="C830" t="n">
+        <v>22</v>
+      </c>
+      <c r="D830" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D830"/>
+  <dimension ref="A1:D831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15267,16 +15267,16 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/06</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C825" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D825" t="n">
         <v>101</v>
@@ -15285,12 +15285,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -15303,12 +15303,12 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -15321,12 +15321,12 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -15339,12 +15339,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -15357,18 +15357,36 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>22</v>
+      </c>
+      <c r="D830" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B830" t="inlineStr">
+      <c r="B831" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C830" t="n">
-        <v>22</v>
-      </c>
-      <c r="D830" t="n">
+      <c r="C831" t="n">
+        <v>22</v>
+      </c>
+      <c r="D831" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D831"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15285,16 +15285,16 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C826" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D826" t="n">
         <v>101</v>
@@ -15303,16 +15303,16 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/09/08</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C827" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D827" t="n">
         <v>101</v>
@@ -15321,16 +15321,16 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/09/08</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C828" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D828" t="n">
         <v>101</v>
@@ -15339,12 +15339,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -15357,12 +15357,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C830" t="n">
@@ -15375,18 +15375,72 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>22</v>
+      </c>
+      <c r="D831" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2027/01/01</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>22</v>
+      </c>
+      <c r="D832" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>22</v>
+      </c>
+      <c r="D833" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B831" t="inlineStr">
+      <c r="B834" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C831" t="n">
-        <v>22</v>
-      </c>
-      <c r="D831" t="n">
+      <c r="C834" t="n">
+        <v>22</v>
+      </c>
+      <c r="D834" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D834"/>
+  <dimension ref="A1:D835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15339,7 +15339,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/08</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="C829" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D829" t="n">
         <v>101</v>
@@ -15357,12 +15357,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C830" t="n">
@@ -15375,12 +15375,12 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -15393,12 +15393,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -15411,12 +15411,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -15429,18 +15429,36 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>22</v>
+      </c>
+      <c r="D834" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B834" t="inlineStr">
+      <c r="B835" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C834" t="n">
-        <v>22</v>
-      </c>
-      <c r="D834" t="n">
+      <c r="C835" t="n">
+        <v>22</v>
+      </c>
+      <c r="D835" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D835"/>
+  <dimension ref="A1:D836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15357,16 +15357,16 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/09</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C830" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D830" t="n">
         <v>101</v>
@@ -15375,12 +15375,12 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -15393,12 +15393,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -15411,12 +15411,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -15429,12 +15429,12 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -15447,18 +15447,36 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>22</v>
+      </c>
+      <c r="D835" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B835" t="inlineStr">
+      <c r="B836" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C835" t="n">
-        <v>22</v>
-      </c>
-      <c r="D835" t="n">
+      <c r="C836" t="n">
+        <v>22</v>
+      </c>
+      <c r="D836" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15375,16 +15375,16 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/09</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C831" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D831" t="n">
         <v>101</v>
@@ -15393,12 +15393,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -15411,12 +15411,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -15429,12 +15429,12 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -15447,12 +15447,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -15465,18 +15465,36 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>22</v>
+      </c>
+      <c r="D836" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B836" t="inlineStr">
+      <c r="B837" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C836" t="n">
-        <v>22</v>
-      </c>
-      <c r="D836" t="n">
+      <c r="C837" t="n">
+        <v>22</v>
+      </c>
+      <c r="D837" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D837"/>
+  <dimension ref="A1:D838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15393,16 +15393,16 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/09</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C832" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D832" t="n">
         <v>101</v>
@@ -15411,12 +15411,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -15429,12 +15429,12 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -15447,12 +15447,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -15465,12 +15465,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C836" t="n">
@@ -15483,18 +15483,36 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>22</v>
+      </c>
+      <c r="D837" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B837" t="inlineStr">
+      <c r="B838" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C837" t="n">
-        <v>22</v>
-      </c>
-      <c r="D837" t="n">
+      <c r="C838" t="n">
+        <v>22</v>
+      </c>
+      <c r="D838" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D838"/>
+  <dimension ref="A1:D840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15411,16 +15411,16 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/10</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C833" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D833" t="n">
         <v>101</v>
@@ -15429,16 +15429,16 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/09/11</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C834" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D834" t="n">
         <v>101</v>
@@ -15447,12 +15447,12 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -15465,12 +15465,12 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C836" t="n">
@@ -15483,12 +15483,12 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -15501,18 +15501,54 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
+          <t>2027/01/01</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>22</v>
+      </c>
+      <c r="D838" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>22</v>
+      </c>
+      <c r="D839" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B838" t="inlineStr">
+      <c r="B840" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C838" t="n">
-        <v>22</v>
-      </c>
-      <c r="D838" t="n">
+      <c r="C840" t="n">
+        <v>22</v>
+      </c>
+      <c r="D840" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D840"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15447,16 +15447,16 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/11</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C835" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D835" t="n">
         <v>101</v>
@@ -15465,16 +15465,16 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/09/11</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C836" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D836" t="n">
         <v>101</v>
@@ -15483,16 +15483,16 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C837" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D837" t="n">
         <v>101</v>
@@ -15501,12 +15501,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -15519,12 +15519,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -15537,18 +15537,72 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>22</v>
+      </c>
+      <c r="D840" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2027/01/01</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>22</v>
+      </c>
+      <c r="D841" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>22</v>
+      </c>
+      <c r="D842" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B840" t="inlineStr">
+      <c r="B843" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C840" t="n">
-        <v>22</v>
-      </c>
-      <c r="D840" t="n">
+      <c r="C843" t="n">
+        <v>22</v>
+      </c>
+      <c r="D843" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D843"/>
+  <dimension ref="A1:D844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15501,16 +15501,16 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C838" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D838" t="n">
         <v>101</v>
@@ -15519,12 +15519,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -15537,12 +15537,12 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C840" t="n">
@@ -15555,12 +15555,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -15573,12 +15573,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -15591,18 +15591,36 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>22</v>
+      </c>
+      <c r="D843" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B843" t="inlineStr">
+      <c r="B844" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C843" t="n">
-        <v>22</v>
-      </c>
-      <c r="D843" t="n">
+      <c r="C844" t="n">
+        <v>22</v>
+      </c>
+      <c r="D844" t="n">
         <v>101</v>
       </c>
     </row>
